--- a/aspnet-core/prototype/领用配送接口FS(2).xlsx
+++ b/aspnet-core/prototype/领用配送接口FS(2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\module-zero-core-template\aspnet-core\prototype\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B9D897-0F7E-45CE-8423-3248119EABF1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE41C552-4E96-4FB4-A988-724B30EF8593}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6948" tabRatio="669" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6945" tabRatio="669" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="目录" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="333">
   <si>
     <t>A-LM-ABAP-WMZC588</t>
   </si>
@@ -134,931 +134,989 @@
   </si>
   <si>
     <t>ATMS</t>
+  </si>
+  <si>
+    <t>─ 588 ─▶</t>
+  </si>
+  <si>
+    <t>▼</t>
+  </si>
+  <si>
+    <t>② WCT · 领用部门
+创建领料配送需求
+多次配送 → 拆解配送需求</t>
+  </si>
+  <si>
+    <t>◀─ 591 ─</t>
+  </si>
+  <si>
+    <t>◀─ 592 ─</t>
+  </si>
+  <si>
+    <t>⑤ WCT · 资材部门
+配送货源试算 · 执行试算
+求解器返回货源建议</t>
+  </si>
+  <si>
+    <t>⑥ WCT 确认货源
+按货源类型分流 ↓
+厂内 / 供应商 / 码头</t>
+  </si>
+  <si>
+    <t>◀─ 593 ─▶</t>
+  </si>
+  <si>
+    <t>◀─ 633 ─</t>
+  </si>
+  <si>
+    <t>─ 666 ─▶</t>
+  </si>
+  <si>
+    <t>◀┄ 预约 ┄</t>
+  </si>
+  <si>
+    <t>⑩ ATMS → SAP
+ATMS 针对短驳计划做预约
+预约信息发送给 SAP</t>
+  </si>
+  <si>
+    <t>─ 638 ─▶</t>
+  </si>
+  <si>
+    <t>⑫ WCT 匹配
+用预约信息匹配短驳计划
+确认该短驳计划绑定了哪些预约号</t>
+  </si>
+  <si>
+    <t>⑬【码头仓库】WCT 调 SAP
+633 货源与预约关系接口
+(LM-INT-WCT-068)
+把预约号同步给 SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">领料单审批状态变更为F时调用接口，发送信息给WCT，发送数据保存
+</t>
+  </si>
+  <si>
+    <t>前台新增查询日志程序，按照条件查询数据，增加重处理按钮，选择行项目，调用接口发送</t>
+  </si>
+  <si>
+    <t>程序增加补发功能，输入工厂+领料单后，如果查询不到发送数据，可以触发接口进行发送</t>
+  </si>
+  <si>
+    <t>输入</t>
+  </si>
+  <si>
+    <t>领料工厂</t>
+  </si>
+  <si>
+    <t>WERKS1</t>
+  </si>
+  <si>
+    <t>CHAR</t>
+  </si>
+  <si>
+    <t>4,0</t>
+  </si>
+  <si>
+    <t>ZLMT00300</t>
+  </si>
+  <si>
+    <t>发料工厂</t>
+  </si>
+  <si>
+    <t>WERKS2</t>
+  </si>
+  <si>
+    <t>ZLMT00301</t>
+  </si>
+  <si>
+    <t>领料单号</t>
+  </si>
+  <si>
+    <t>LLSQD</t>
+  </si>
+  <si>
+    <t>10，0</t>
+  </si>
+  <si>
+    <t>领料单行</t>
+  </si>
+  <si>
+    <t>LLPOS</t>
+  </si>
+  <si>
+    <t>NUMC</t>
+  </si>
+  <si>
+    <t>5,0</t>
+  </si>
+  <si>
+    <t>物料号</t>
+  </si>
+  <si>
+    <t>MATNR</t>
+  </si>
+  <si>
+    <t>18，0</t>
+  </si>
+  <si>
+    <t>领用数量</t>
+  </si>
+  <si>
+    <t>MENGE</t>
+  </si>
+  <si>
+    <t>QUAN</t>
+  </si>
+  <si>
+    <t>13,3</t>
+  </si>
+  <si>
+    <t>单位</t>
+  </si>
+  <si>
+    <t>MEINS</t>
+  </si>
+  <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>3,0</t>
+  </si>
+  <si>
+    <t>批次</t>
+  </si>
+  <si>
+    <t>CHARG</t>
+  </si>
+  <si>
+    <t>认证种类</t>
+  </si>
+  <si>
+    <t>RZZL</t>
+  </si>
+  <si>
+    <t>30，0</t>
+  </si>
+  <si>
+    <t>收货库存地点</t>
+  </si>
+  <si>
+    <t>UMLGO</t>
+  </si>
+  <si>
+    <t>MES仓位</t>
+  </si>
+  <si>
+    <t>MESCW</t>
+  </si>
+  <si>
+    <t>20260605新增</t>
+  </si>
+  <si>
+    <t>领料单创建日期</t>
+  </si>
+  <si>
+    <t>LLSQRQ</t>
+  </si>
+  <si>
+    <t>DATS</t>
+  </si>
+  <si>
+    <t>8，0</t>
+  </si>
+  <si>
+    <t>是否配送</t>
+  </si>
+  <si>
+    <t>SFPS</t>
+  </si>
+  <si>
+    <t>1,0</t>
+  </si>
+  <si>
+    <t>结合领料单修改</t>
+  </si>
+  <si>
+    <t>配送方式</t>
+  </si>
+  <si>
+    <t>ZPSFS</t>
+  </si>
+  <si>
+    <t>需求配送截止日</t>
+  </si>
+  <si>
+    <t>PSRQ</t>
+  </si>
+  <si>
+    <t>需求配送时间段</t>
+  </si>
+  <si>
+    <t>ZPSSJD</t>
+  </si>
+  <si>
+    <t>20，0</t>
+  </si>
+  <si>
+    <t>申请人</t>
+  </si>
+  <si>
+    <t>PERNR</t>
+  </si>
+  <si>
+    <t>电话</t>
+  </si>
+  <si>
+    <t>TELNR</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>BEIZHU</t>
+  </si>
+  <si>
+    <t>255,0</t>
+  </si>
+  <si>
+    <t>特殊库存</t>
+  </si>
+  <si>
+    <t>SOBKZ</t>
+  </si>
+  <si>
+    <t>新增</t>
+  </si>
+  <si>
+    <t>申请部门</t>
+  </si>
+  <si>
+    <t>DEPRT</t>
+  </si>
+  <si>
+    <t>8,0</t>
+  </si>
+  <si>
+    <t>20260611新增</t>
+  </si>
+  <si>
+    <t>输出</t>
+  </si>
+  <si>
+    <t>MSG_TYPE</t>
+  </si>
+  <si>
+    <t>返回标识</t>
+  </si>
+  <si>
+    <t>CHAR 1</t>
+  </si>
+  <si>
+    <t>S 成功 E失败</t>
+  </si>
+  <si>
+    <t>MSG_TXT</t>
+  </si>
+  <si>
+    <t>返回消息</t>
+  </si>
+  <si>
+    <t>CHAR 220</t>
+  </si>
+  <si>
+    <t>实时实际报错消息</t>
+  </si>
+  <si>
+    <t>库存接口</t>
+  </si>
+  <si>
+    <t>工厂</t>
+  </si>
+  <si>
+    <t>WERKS</t>
+  </si>
+  <si>
+    <t>多项输入</t>
+  </si>
+  <si>
+    <t>必填</t>
+  </si>
+  <si>
+    <t>LQUA</t>
+  </si>
+  <si>
+    <t>库存地点</t>
+  </si>
+  <si>
+    <t>LGORT</t>
+  </si>
+  <si>
+    <t>10,0</t>
+  </si>
+  <si>
+    <t>库存类型</t>
+  </si>
+  <si>
+    <t>BESTQ</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>GESME</t>
+  </si>
+  <si>
+    <t>仓库号</t>
+  </si>
+  <si>
+    <t>LGNUM</t>
+  </si>
+  <si>
+    <t>仓储类型</t>
+  </si>
+  <si>
+    <t>LGTYP</t>
+  </si>
+  <si>
+    <t>仓位</t>
+  </si>
+  <si>
+    <t>LGPLA</t>
+  </si>
+  <si>
+    <t>30,0</t>
+  </si>
+  <si>
+    <t>分类ZPTP002，特性ZPU003</t>
+  </si>
+  <si>
+    <t>收货日期</t>
+  </si>
+  <si>
+    <t>LWEDT</t>
+  </si>
+  <si>
+    <t>MCH1</t>
+  </si>
+  <si>
+    <t>内向交货单</t>
+  </si>
+  <si>
+    <t>VBELN</t>
+  </si>
+  <si>
+    <t>根据工厂料号及批次，查询MSEG 101凭证，获取VBELN_IM，在表ZLMT00780查询免堆日期及延滞费以及转栈日期</t>
+  </si>
+  <si>
+    <t>交货单行项目</t>
+  </si>
+  <si>
+    <t>VBELP</t>
+  </si>
+  <si>
+    <t>6,0</t>
+  </si>
+  <si>
+    <t>装运编号</t>
+  </si>
+  <si>
+    <t>TKNUM</t>
+  </si>
+  <si>
+    <t>装运项目</t>
+  </si>
+  <si>
+    <t>TPNUM</t>
+  </si>
+  <si>
+    <t>公司代码</t>
+  </si>
+  <si>
+    <t>BUKRS</t>
+  </si>
+  <si>
+    <t>船名</t>
+  </si>
+  <si>
+    <t>ZZCM</t>
+  </si>
+  <si>
+    <t>20,0</t>
+  </si>
+  <si>
+    <t>航次</t>
+  </si>
+  <si>
+    <t>ZZHC</t>
+  </si>
+  <si>
+    <t>15,0</t>
+  </si>
+  <si>
+    <t>码头免堆到日期</t>
+  </si>
+  <si>
+    <t>MTMD_DQR</t>
+  </si>
+  <si>
+    <t>逾期延滞费</t>
+  </si>
+  <si>
+    <t>YQYZ_FEE</t>
+  </si>
+  <si>
+    <t>DEC</t>
+  </si>
+  <si>
+    <t>10,2</t>
+  </si>
+  <si>
+    <t>转栈日期</t>
+  </si>
+  <si>
+    <t>ZZDATE</t>
+  </si>
+  <si>
+    <t>特殊库存标识</t>
+  </si>
+  <si>
+    <t>特殊库存编号</t>
+  </si>
+  <si>
+    <t>SONUM</t>
+  </si>
+  <si>
+    <t>16，0</t>
+  </si>
+  <si>
+    <t>是否免检</t>
+  </si>
+  <si>
+    <t>ZNOCHK</t>
+  </si>
+  <si>
+    <t>Y/N</t>
+  </si>
+  <si>
+    <t>库存类型为Q质检库存时，根据批次特性小料号查询表ZPTPT50070-ZNOCHK Y为免检，如果相同小料号有多条记录，以时间最新的为准</t>
+  </si>
+  <si>
+    <t>检验时间</t>
+  </si>
+  <si>
+    <t>JYSJ</t>
+  </si>
+  <si>
+    <t>13,0</t>
+  </si>
+  <si>
+    <t>如果物料不免检，以下检验时间获取逻辑，获取历史检验时间，取平均值</t>
+  </si>
+  <si>
+    <t>检验时间获取逻辑：</t>
+  </si>
+  <si>
+    <t>1、取主检验批数据： 根据物料+工厂 至ZPTPT50070表取ZLOT(主检验批)，条件输入物料=ZPTPT50070-MATNR，输入工厂=WERKS  
+2、取取样开始时间：根据主检验批至ZPTPT50196-ZLOT and ZPTPT50196-ZMESENDV= 'S'(取样开始)取ZCZRQ操作日期和ZCZSJ操作时间，
+3、取检验决策时 间：根据主检验批 取ZPTPT50130-VDATUM 日期   ZPTPT50130-VEZEITERF 时间  ZPTPT50130-ZRPTSTG有3取3  没3取2  （3复检，2初检）； 
+4；检验时间 = 检验决策时间-取样开始时间 </t>
+  </si>
+  <si>
+    <t>预约信息接口</t>
+  </si>
+  <si>
+    <t>根据输入的工厂物料号，查询ZLMT00040中，预约到厂日不早于查询日期的预约数据</t>
+  </si>
+  <si>
+    <t>YYSHD</t>
+  </si>
+  <si>
+    <t>预约送货单号</t>
+  </si>
+  <si>
+    <t>交货</t>
+  </si>
+  <si>
+    <t>POSNR</t>
+  </si>
+  <si>
+    <t>交货项目</t>
+  </si>
+  <si>
+    <t>PLAN_A_F</t>
+  </si>
+  <si>
+    <t>厂区</t>
+  </si>
+  <si>
+    <t>PLAN_A_T</t>
+  </si>
+  <si>
+    <t>YYZT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">预约状态 </t>
+  </si>
+  <si>
+    <t>EBELN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">采购凭证号 </t>
+  </si>
+  <si>
+    <t>EBELP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">采购凭证的项目编号 </t>
+  </si>
+  <si>
+    <t>物料编号</t>
+  </si>
+  <si>
+    <t>YSFS</t>
+  </si>
+  <si>
+    <t>运输工具</t>
+  </si>
+  <si>
+    <t>批号</t>
+  </si>
+  <si>
+    <t>CCMC</t>
+  </si>
+  <si>
+    <t>车/船名</t>
+  </si>
+  <si>
+    <t>CHEX</t>
+  </si>
+  <si>
+    <t>车型</t>
+  </si>
+  <si>
+    <t>YYLX</t>
+  </si>
+  <si>
+    <t>预约类型</t>
+  </si>
+  <si>
+    <t>BZLX</t>
+  </si>
+  <si>
+    <t>包装类型</t>
+  </si>
+  <si>
+    <t>VLTYP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">源仓储类型 </t>
+  </si>
+  <si>
+    <t>YYSHL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">预约送货量 </t>
+  </si>
+  <si>
+    <t>基本计量单位</t>
+  </si>
+  <si>
+    <t>YYJS</t>
+  </si>
+  <si>
+    <t>预约件数</t>
+  </si>
+  <si>
+    <t>DJBZZ</t>
+  </si>
+  <si>
+    <t>单件标准重量</t>
+  </si>
+  <si>
+    <t>JZXGG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">集装箱规格 </t>
+  </si>
+  <si>
+    <t>JZXSL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">集装箱数量 </t>
+  </si>
+  <si>
+    <t>SYXL</t>
+  </si>
+  <si>
+    <t>剩余箱量</t>
+  </si>
+  <si>
+    <t>DJBZWZ</t>
+  </si>
+  <si>
+    <t>单件包装物重</t>
+  </si>
+  <si>
+    <t>YYBZZ</t>
+  </si>
+  <si>
+    <t>预约包装物总重</t>
+  </si>
+  <si>
+    <t>SCDAT</t>
+  </si>
+  <si>
+    <t>生产日期</t>
+  </si>
+  <si>
+    <t>BZDAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保质期 </t>
+  </si>
+  <si>
+    <t>DCDAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">预约到厂日 </t>
+  </si>
+  <si>
+    <t>HJDAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">货架寿命到期日 </t>
+  </si>
+  <si>
+    <t>ZCDAT</t>
+  </si>
+  <si>
+    <t>最迟有效到厂日</t>
+  </si>
+  <si>
+    <t>RZBL</t>
+  </si>
+  <si>
+    <t>认证比例</t>
+  </si>
+  <si>
+    <t>RZH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">认证号 </t>
+  </si>
+  <si>
+    <t>JZXH</t>
+  </si>
+  <si>
+    <t>集装箱号</t>
+  </si>
+  <si>
+    <t>SJXM</t>
+  </si>
+  <si>
+    <t>司机姓名</t>
+  </si>
+  <si>
+    <t>SJDH</t>
+  </si>
+  <si>
+    <t>司机电话</t>
+  </si>
+  <si>
+    <t>短驳运输计划</t>
+  </si>
+  <si>
+    <t>ZQFH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">铅封号 </t>
+  </si>
+  <si>
+    <t>TDH</t>
+  </si>
+  <si>
+    <t>总单号/提运单号</t>
+  </si>
+  <si>
+    <t>PACK_NO</t>
+  </si>
+  <si>
+    <t>配载编号</t>
+  </si>
+  <si>
+    <t>BOXTYP</t>
+  </si>
+  <si>
+    <t>箱型</t>
+  </si>
+  <si>
+    <t>MILEAGE</t>
+  </si>
+  <si>
+    <t>里程</t>
+  </si>
+  <si>
+    <t>MILEUNIT</t>
+  </si>
+  <si>
+    <t>里程单位</t>
+  </si>
+  <si>
+    <t>.INCLUDE</t>
+  </si>
+  <si>
+    <t>STRU</t>
+  </si>
+  <si>
+    <t>修改记录</t>
+  </si>
+  <si>
+    <t>CNAME_CRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">记录创建者 </t>
+  </si>
+  <si>
+    <t>CDATE_CRE</t>
+  </si>
+  <si>
+    <t>创建日期</t>
+  </si>
+  <si>
+    <t>CTIME_CRE</t>
+  </si>
+  <si>
+    <t>TIMS</t>
+  </si>
+  <si>
+    <t>创建时间</t>
+  </si>
+  <si>
+    <t>UNAME_UPD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">记录修改者 </t>
+  </si>
+  <si>
+    <t>UDATE_UPD</t>
+  </si>
+  <si>
+    <t>修改日期</t>
+  </si>
+  <si>
+    <t>UTIME_UPD</t>
+  </si>
+  <si>
+    <t>修改时间</t>
+  </si>
+  <si>
+    <t>DEL_IND</t>
+  </si>
+  <si>
+    <t>删除标记</t>
+  </si>
+  <si>
+    <t>免检</t>
+  </si>
+  <si>
+    <t>配送需求单</t>
+  </si>
+  <si>
+    <t>PSXQD</t>
+  </si>
+  <si>
+    <t>配送需求单行</t>
+  </si>
+  <si>
+    <t>PSXQH</t>
+  </si>
+  <si>
+    <t>备注：可能没有，字段保留，可以为空</t>
+  </si>
+  <si>
+    <t>18,0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 WCT根据领料单行项目拆分配送需求，生成后传输SAP根据领料单生成拣配单行
+2 ZLMT00307增加字段“配送需求单”“配送需求行”
+3 根据配送需求生成拣配单后，字段信息存表 </t>
+  </si>
+  <si>
+    <t>拣配数量</t>
+  </si>
+  <si>
+    <t>ZJPSL</t>
+  </si>
+  <si>
+    <t>成功的话消息“配送需求&amp;行XX，拣配单&amp;行XX已生成”</t>
+  </si>
+  <si>
+    <t>配送计划完成，过账接口</t>
+  </si>
+  <si>
+    <t>WCT确定货源，如果是短驳进厂的或者门到门进厂的，将货源的领料单及行项目和货源匹配的预约单号的关系发送给SAP</t>
+  </si>
+  <si>
+    <t>拣配单号</t>
+  </si>
+  <si>
+    <t>LLJPD</t>
+  </si>
+  <si>
+    <t>WCT确定货源信息之后，如果货源是送货预约的或者短驳预约的，将关系传输至SAP，用于采购收货策略确定。
+SAP新建一张自建表“领用配送货源与预约信息关系表”，保存数据。</t>
+  </si>
+  <si>
+    <t>拣配单行</t>
+  </si>
+  <si>
+    <t>LLJPDHXM</t>
+  </si>
+  <si>
+    <t>预约单号</t>
+  </si>
+  <si>
+    <t>内向交货单行</t>
+  </si>
+  <si>
+    <t>LM-INT-037接口接收到ATMS预约信息之后，ZLMT04660表中启用控制塔的工厂的数据触发此接口发送给WCT</t>
+  </si>
+  <si>
+    <t>同链接输出内容</t>
+  </si>
+  <si>
+    <t>短驳计划接口，WCT发送ATMS</t>
+  </si>
+  <si>
+    <t>预约匹配短驳计划条件：</t>
+  </si>
+  <si>
+    <t>分配数量</t>
+  </si>
+  <si>
+    <t>ZFPSL</t>
+  </si>
+  <si>
+    <t>需求配送日</t>
+  </si>
+  <si>
+    <t>PSJZRQ</t>
+  </si>
+  <si>
+    <t>短驳计划号</t>
+  </si>
+  <si>
+    <t>DBJH</t>
+  </si>
+  <si>
+    <t>WCT生成</t>
+  </si>
+  <si>
+    <t>成功的话消息“返回短驳计划号”</t>
+  </si>
+  <si>
+    <t>预约信息发送WCT接口</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发货库存地点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LGORT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260703新增</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>① SAP → WCT
 588 领料配送需求同步
 (LM-INT-WCT-064)
 领料单审批为F时发送</t>
-  </si>
-  <si>
-    <t>─ 588 ─▶</t>
-  </si>
-  <si>
-    <t>▼</t>
-  </si>
-  <si>
-    <t>② WCT · 领用部门
-创建领料配送需求
-多次配送 → 拆解配送需求</t>
-  </si>
-  <si>
-    <t>◀─ 591 ─</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>③ WCT 调 SAP
 591 库存接口(含589检验/590免堆)
 (LM-INT-WCT-063)
 取候选货源 ←返回</t>
-  </si>
-  <si>
-    <t>◀─ 592 ─</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>④ WCT 调 SAP
 592 预约信息接口
 (LM-INT-WCT-065)
 取供应商预约 ←返回</t>
-  </si>
-  <si>
-    <t>⑤ WCT · 资材部门
-配送货源试算 · 执行试算
-求解器返回货源建议</t>
-  </si>
-  <si>
-    <t>⑥ WCT 确认货源
-按货源类型分流 ↓
-厂内 / 供应商 / 码头</t>
-  </si>
-  <si>
-    <t>◀─ 593 ─▶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>⑦【厂内资材库】WCT 调 SAP
 593 拣配计划接口 创建拣配计划
 (LM-INT-WCT-066) → 返回拣配单号
 物料有装载限制 → 拆解为多个配送单</t>
-  </si>
-  <si>
-    <t>◀─ 633 ─</t>
-  </si>
-  <si>
-    <t>⑧【供应商送货】WCT 调 SAP
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">⑧【供应商送货】WCT 调 SAP
 633 货源与预约关系接口
 (LM-INT-WCT-068)
-绑定预约号(领料行 ↔ 预约号)</t>
+绑定预约号(领料行 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>↔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 预约号)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>⑨【码头仓库】WCT 调 ATMS
 666 短驳计划接口
 创建短驳计划</t>
-  </si>
-  <si>
-    <t>─ 666 ─▶</t>
-  </si>
-  <si>
-    <t>◀┄ 预约 ┄</t>
-  </si>
-  <si>
-    <t>⑩ ATMS → SAP
-ATMS 针对短驳计划做预约
-预约信息发送给 SAP</t>
-  </si>
-  <si>
-    <t>⑪ SAP → WCT
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="1"/>
+      </rPr>
+      <t>⑪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> SAP → WCT
 638 预约信息同步接口
 (LM-INT-WCT-070)
 把ATMS预约信息同步给WCT</t>
-  </si>
-  <si>
-    <t>─ 638 ─▶</t>
-  </si>
-  <si>
-    <t>⑫ WCT 匹配
-用预约信息匹配短驳计划
-确认该短驳计划绑定了哪些预约号</t>
-  </si>
-  <si>
-    <t>⑬【码头仓库】WCT 调 SAP
-633 货源与预约关系接口
-(LM-INT-WCT-068)
-把预约号同步给 SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">领料单审批状态变更为F时调用接口，发送信息给WCT，发送数据保存
-</t>
-  </si>
-  <si>
-    <t>前台新增查询日志程序，按照条件查询数据，增加重处理按钮，选择行项目，调用接口发送</t>
-  </si>
-  <si>
-    <t>程序增加补发功能，输入工厂+领料单后，如果查询不到发送数据，可以触发接口进行发送</t>
-  </si>
-  <si>
-    <t>输入</t>
-  </si>
-  <si>
-    <t>领料工厂</t>
-  </si>
-  <si>
-    <t>WERKS1</t>
-  </si>
-  <si>
-    <t>CHAR</t>
-  </si>
-  <si>
-    <t>4,0</t>
-  </si>
-  <si>
-    <t>ZLMT00300</t>
-  </si>
-  <si>
-    <t>发料工厂</t>
-  </si>
-  <si>
-    <t>WERKS2</t>
-  </si>
-  <si>
-    <t>ZLMT00301</t>
-  </si>
-  <si>
-    <t>领料单号</t>
-  </si>
-  <si>
-    <t>LLSQD</t>
-  </si>
-  <si>
-    <t>10，0</t>
-  </si>
-  <si>
-    <t>领料单行</t>
-  </si>
-  <si>
-    <t>LLPOS</t>
-  </si>
-  <si>
-    <t>NUMC</t>
-  </si>
-  <si>
-    <t>5,0</t>
-  </si>
-  <si>
-    <t>物料号</t>
-  </si>
-  <si>
-    <t>MATNR</t>
-  </si>
-  <si>
-    <t>18，0</t>
-  </si>
-  <si>
-    <t>领用数量</t>
-  </si>
-  <si>
-    <t>MENGE</t>
-  </si>
-  <si>
-    <t>QUAN</t>
-  </si>
-  <si>
-    <t>13,3</t>
-  </si>
-  <si>
-    <t>单位</t>
-  </si>
-  <si>
-    <t>MEINS</t>
-  </si>
-  <si>
-    <t>UNIT</t>
-  </si>
-  <si>
-    <t>3,0</t>
-  </si>
-  <si>
-    <t>批次</t>
-  </si>
-  <si>
-    <t>CHARG</t>
-  </si>
-  <si>
-    <t>认证种类</t>
-  </si>
-  <si>
-    <t>RZZL</t>
-  </si>
-  <si>
-    <t>30，0</t>
-  </si>
-  <si>
-    <t>收货库存地点</t>
-  </si>
-  <si>
-    <t>UMLGO</t>
-  </si>
-  <si>
-    <t>MES仓位</t>
-  </si>
-  <si>
-    <t>MESCW</t>
-  </si>
-  <si>
-    <t>20260605新增</t>
-  </si>
-  <si>
-    <t>领料单创建日期</t>
-  </si>
-  <si>
-    <t>LLSQRQ</t>
-  </si>
-  <si>
-    <t>DATS</t>
-  </si>
-  <si>
-    <t>8，0</t>
-  </si>
-  <si>
-    <t>是否配送</t>
-  </si>
-  <si>
-    <t>SFPS</t>
-  </si>
-  <si>
-    <t>1,0</t>
-  </si>
-  <si>
-    <t>结合领料单修改</t>
-  </si>
-  <si>
-    <t>配送方式</t>
-  </si>
-  <si>
-    <t>ZPSFS</t>
-  </si>
-  <si>
-    <t>需求配送截止日</t>
-  </si>
-  <si>
-    <t>PSRQ</t>
-  </si>
-  <si>
-    <t>需求配送时间段</t>
-  </si>
-  <si>
-    <t>ZPSSJD</t>
-  </si>
-  <si>
-    <t>20，0</t>
-  </si>
-  <si>
-    <t>申请人</t>
-  </si>
-  <si>
-    <t>PERNR</t>
-  </si>
-  <si>
-    <t>电话</t>
-  </si>
-  <si>
-    <t>TELNR</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>BEIZHU</t>
-  </si>
-  <si>
-    <t>255,0</t>
-  </si>
-  <si>
-    <t>特殊库存</t>
-  </si>
-  <si>
-    <t>SOBKZ</t>
-  </si>
-  <si>
-    <t>新增</t>
-  </si>
-  <si>
-    <t>申请部门</t>
-  </si>
-  <si>
-    <t>DEPRT</t>
-  </si>
-  <si>
-    <t>8,0</t>
-  </si>
-  <si>
-    <t>20260611新增</t>
-  </si>
-  <si>
-    <t>输出</t>
-  </si>
-  <si>
-    <t>MSG_TYPE</t>
-  </si>
-  <si>
-    <t>返回标识</t>
-  </si>
-  <si>
-    <t>CHAR 1</t>
-  </si>
-  <si>
-    <t>S 成功 E失败</t>
-  </si>
-  <si>
-    <t>MSG_TXT</t>
-  </si>
-  <si>
-    <t>返回消息</t>
-  </si>
-  <si>
-    <t>CHAR 220</t>
-  </si>
-  <si>
-    <t>实时实际报错消息</t>
-  </si>
-  <si>
-    <t>库存接口</t>
-  </si>
-  <si>
-    <t>工厂</t>
-  </si>
-  <si>
-    <t>WERKS</t>
-  </si>
-  <si>
-    <t>多项输入</t>
-  </si>
-  <si>
-    <t>必填</t>
-  </si>
-  <si>
-    <t>LQUA</t>
-  </si>
-  <si>
-    <t>库存地点</t>
-  </si>
-  <si>
-    <t>LGORT</t>
-  </si>
-  <si>
-    <t>10,0</t>
-  </si>
-  <si>
-    <t>库存类型</t>
-  </si>
-  <si>
-    <t>BESTQ</t>
-  </si>
-  <si>
-    <t>数量</t>
-  </si>
-  <si>
-    <t>GESME</t>
-  </si>
-  <si>
-    <t>仓库号</t>
-  </si>
-  <si>
-    <t>LGNUM</t>
-  </si>
-  <si>
-    <t>仓储类型</t>
-  </si>
-  <si>
-    <t>LGTYP</t>
-  </si>
-  <si>
-    <t>仓位</t>
-  </si>
-  <si>
-    <t>LGPLA</t>
-  </si>
-  <si>
-    <t>30,0</t>
-  </si>
-  <si>
-    <t>分类ZPTP002，特性ZPU003</t>
-  </si>
-  <si>
-    <t>收货日期</t>
-  </si>
-  <si>
-    <t>LWEDT</t>
-  </si>
-  <si>
-    <t>MCH1</t>
-  </si>
-  <si>
-    <t>内向交货单</t>
-  </si>
-  <si>
-    <t>VBELN</t>
-  </si>
-  <si>
-    <t>根据工厂料号及批次，查询MSEG 101凭证，获取VBELN_IM，在表ZLMT00780查询免堆日期及延滞费以及转栈日期</t>
-  </si>
-  <si>
-    <t>交货单行项目</t>
-  </si>
-  <si>
-    <t>VBELP</t>
-  </si>
-  <si>
-    <t>6,0</t>
-  </si>
-  <si>
-    <t>装运编号</t>
-  </si>
-  <si>
-    <t>TKNUM</t>
-  </si>
-  <si>
-    <t>装运项目</t>
-  </si>
-  <si>
-    <t>TPNUM</t>
-  </si>
-  <si>
-    <t>公司代码</t>
-  </si>
-  <si>
-    <t>BUKRS</t>
-  </si>
-  <si>
-    <t>船名</t>
-  </si>
-  <si>
-    <t>ZZCM</t>
-  </si>
-  <si>
-    <t>20,0</t>
-  </si>
-  <si>
-    <t>航次</t>
-  </si>
-  <si>
-    <t>ZZHC</t>
-  </si>
-  <si>
-    <t>15,0</t>
-  </si>
-  <si>
-    <t>码头免堆到日期</t>
-  </si>
-  <si>
-    <t>MTMD_DQR</t>
-  </si>
-  <si>
-    <t>逾期延滞费</t>
-  </si>
-  <si>
-    <t>YQYZ_FEE</t>
-  </si>
-  <si>
-    <t>DEC</t>
-  </si>
-  <si>
-    <t>10,2</t>
-  </si>
-  <si>
-    <t>转栈日期</t>
-  </si>
-  <si>
-    <t>ZZDATE</t>
-  </si>
-  <si>
-    <t>特殊库存标识</t>
-  </si>
-  <si>
-    <t>特殊库存编号</t>
-  </si>
-  <si>
-    <t>SONUM</t>
-  </si>
-  <si>
-    <t>16，0</t>
-  </si>
-  <si>
-    <t>是否免检</t>
-  </si>
-  <si>
-    <t>ZNOCHK</t>
-  </si>
-  <si>
-    <t>Y/N</t>
-  </si>
-  <si>
-    <t>库存类型为Q质检库存时，根据批次特性小料号查询表ZPTPT50070-ZNOCHK Y为免检，如果相同小料号有多条记录，以时间最新的为准</t>
-  </si>
-  <si>
-    <t>检验时间</t>
-  </si>
-  <si>
-    <t>JYSJ</t>
-  </si>
-  <si>
-    <t>13,0</t>
-  </si>
-  <si>
-    <t>如果物料不免检，以下检验时间获取逻辑，获取历史检验时间，取平均值</t>
-  </si>
-  <si>
-    <t>检验时间获取逻辑：</t>
-  </si>
-  <si>
-    <t>1、取主检验批数据： 根据物料+工厂 至ZPTPT50070表取ZLOT(主检验批)，条件输入物料=ZPTPT50070-MATNR，输入工厂=WERKS  
-2、取取样开始时间：根据主检验批至ZPTPT50196-ZLOT and ZPTPT50196-ZMESENDV= 'S'(取样开始)取ZCZRQ操作日期和ZCZSJ操作时间，
-3、取检验决策时 间：根据主检验批 取ZPTPT50130-VDATUM 日期   ZPTPT50130-VEZEITERF 时间  ZPTPT50130-ZRPTSTG有3取3  没3取2  （3复检，2初检）； 
-4；检验时间 = 检验决策时间-取样开始时间 </t>
-  </si>
-  <si>
-    <t>预约信息接口</t>
-  </si>
-  <si>
-    <t>根据输入的工厂物料号，查询ZLMT00040中，预约到厂日不早于查询日期的预约数据</t>
-  </si>
-  <si>
-    <t>YYSHD</t>
-  </si>
-  <si>
-    <t>预约送货单号</t>
-  </si>
-  <si>
-    <t>交货</t>
-  </si>
-  <si>
-    <t>POSNR</t>
-  </si>
-  <si>
-    <t>交货项目</t>
-  </si>
-  <si>
-    <t>PLAN_A_F</t>
-  </si>
-  <si>
-    <t>厂区</t>
-  </si>
-  <si>
-    <t>PLAN_A_T</t>
-  </si>
-  <si>
-    <t>YYZT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">预约状态 </t>
-  </si>
-  <si>
-    <t>EBELN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">采购凭证号 </t>
-  </si>
-  <si>
-    <t>EBELP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">采购凭证的项目编号 </t>
-  </si>
-  <si>
-    <t>物料编号</t>
-  </si>
-  <si>
-    <t>YSFS</t>
-  </si>
-  <si>
-    <t>运输工具</t>
-  </si>
-  <si>
-    <t>批号</t>
-  </si>
-  <si>
-    <t>CCMC</t>
-  </si>
-  <si>
-    <t>车/船名</t>
-  </si>
-  <si>
-    <t>CHEX</t>
-  </si>
-  <si>
-    <t>车型</t>
-  </si>
-  <si>
-    <t>YYLX</t>
-  </si>
-  <si>
-    <t>预约类型</t>
-  </si>
-  <si>
-    <t>BZLX</t>
-  </si>
-  <si>
-    <t>包装类型</t>
-  </si>
-  <si>
-    <t>VLTYP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">源仓储类型 </t>
-  </si>
-  <si>
-    <t>YYSHL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">预约送货量 </t>
-  </si>
-  <si>
-    <t>基本计量单位</t>
-  </si>
-  <si>
-    <t>YYJS</t>
-  </si>
-  <si>
-    <t>预约件数</t>
-  </si>
-  <si>
-    <t>DJBZZ</t>
-  </si>
-  <si>
-    <t>单件标准重量</t>
-  </si>
-  <si>
-    <t>JZXGG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">集装箱规格 </t>
-  </si>
-  <si>
-    <t>JZXSL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">集装箱数量 </t>
-  </si>
-  <si>
-    <t>SYXL</t>
-  </si>
-  <si>
-    <t>剩余箱量</t>
-  </si>
-  <si>
-    <t>DJBZWZ</t>
-  </si>
-  <si>
-    <t>单件包装物重</t>
-  </si>
-  <si>
-    <t>YYBZZ</t>
-  </si>
-  <si>
-    <t>预约包装物总重</t>
-  </si>
-  <si>
-    <t>SCDAT</t>
-  </si>
-  <si>
-    <t>生产日期</t>
-  </si>
-  <si>
-    <t>BZDAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">保质期 </t>
-  </si>
-  <si>
-    <t>DCDAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">预约到厂日 </t>
-  </si>
-  <si>
-    <t>HJDAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">货架寿命到期日 </t>
-  </si>
-  <si>
-    <t>ZCDAT</t>
-  </si>
-  <si>
-    <t>最迟有效到厂日</t>
-  </si>
-  <si>
-    <t>RZBL</t>
-  </si>
-  <si>
-    <t>认证比例</t>
-  </si>
-  <si>
-    <t>RZH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">认证号 </t>
-  </si>
-  <si>
-    <t>JZXH</t>
-  </si>
-  <si>
-    <t>集装箱号</t>
-  </si>
-  <si>
-    <t>SJXM</t>
-  </si>
-  <si>
-    <t>司机姓名</t>
-  </si>
-  <si>
-    <t>SJDH</t>
-  </si>
-  <si>
-    <t>司机电话</t>
-  </si>
-  <si>
-    <t>短驳运输计划</t>
-  </si>
-  <si>
-    <t>ZQFH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">铅封号 </t>
-  </si>
-  <si>
-    <t>TDH</t>
-  </si>
-  <si>
-    <t>总单号/提运单号</t>
-  </si>
-  <si>
-    <t>PACK_NO</t>
-  </si>
-  <si>
-    <t>配载编号</t>
-  </si>
-  <si>
-    <t>BOXTYP</t>
-  </si>
-  <si>
-    <t>箱型</t>
-  </si>
-  <si>
-    <t>MILEAGE</t>
-  </si>
-  <si>
-    <t>里程</t>
-  </si>
-  <si>
-    <t>MILEUNIT</t>
-  </si>
-  <si>
-    <t>里程单位</t>
-  </si>
-  <si>
-    <t>.INCLUDE</t>
-  </si>
-  <si>
-    <t>STRU</t>
-  </si>
-  <si>
-    <t>修改记录</t>
-  </si>
-  <si>
-    <t>CNAME_CRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">记录创建者 </t>
-  </si>
-  <si>
-    <t>CDATE_CRE</t>
-  </si>
-  <si>
-    <t>创建日期</t>
-  </si>
-  <si>
-    <t>CTIME_CRE</t>
-  </si>
-  <si>
-    <t>TIMS</t>
-  </si>
-  <si>
-    <t>创建时间</t>
-  </si>
-  <si>
-    <t>UNAME_UPD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">记录修改者 </t>
-  </si>
-  <si>
-    <t>UDATE_UPD</t>
-  </si>
-  <si>
-    <t>修改日期</t>
-  </si>
-  <si>
-    <t>UTIME_UPD</t>
-  </si>
-  <si>
-    <t>修改时间</t>
-  </si>
-  <si>
-    <t>DEL_IND</t>
-  </si>
-  <si>
-    <t>删除标记</t>
-  </si>
-  <si>
-    <t>免检</t>
-  </si>
-  <si>
-    <t>配送需求单</t>
-  </si>
-  <si>
-    <t>PSXQD</t>
-  </si>
-  <si>
-    <t>配送需求单行</t>
-  </si>
-  <si>
-    <t>PSXQH</t>
-  </si>
-  <si>
-    <t>备注：可能没有，字段保留，可以为空</t>
-  </si>
-  <si>
-    <t>18,0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 WCT根据领料单行项目拆分配送需求，生成后传输SAP根据领料单生成拣配单行
-2 ZLMT00307增加字段“配送需求单”“配送需求行”
-3 根据配送需求生成拣配单后，字段信息存表 </t>
-  </si>
-  <si>
-    <t>拣配数量</t>
-  </si>
-  <si>
-    <t>ZJPSL</t>
-  </si>
-  <si>
-    <t>成功的话消息“配送需求&amp;行XX，拣配单&amp;行XX已生成”</t>
-  </si>
-  <si>
-    <t>配送计划完成，过账接口</t>
-  </si>
-  <si>
-    <t>WCT确定货源，如果是短驳进厂的或者门到门进厂的，将货源的领料单及行项目和货源匹配的预约单号的关系发送给SAP</t>
-  </si>
-  <si>
-    <t>拣配单号</t>
-  </si>
-  <si>
-    <t>LLJPD</t>
-  </si>
-  <si>
-    <t>WCT确定货源信息之后，如果货源是送货预约的或者短驳预约的，将关系传输至SAP，用于采购收货策略确定。
-SAP新建一张自建表“领用配送货源与预约信息关系表”，保存数据。</t>
-  </si>
-  <si>
-    <t>拣配单行</t>
-  </si>
-  <si>
-    <t>LLJPDHXM</t>
-  </si>
-  <si>
-    <t>预约单号</t>
-  </si>
-  <si>
-    <t>内向交货单行</t>
-  </si>
-  <si>
-    <t>LM-INT-037接口接收到ATMS预约信息之后，ZLMT04660表中启用控制塔的工厂的数据触发此接口发送给WCT</t>
-  </si>
-  <si>
-    <t>同链接输出内容</t>
-  </si>
-  <si>
-    <t>短驳计划接口，WCT发送ATMS</t>
-  </si>
-  <si>
-    <t>预约匹配短驳计划条件：</t>
-  </si>
-  <si>
-    <t>分配数量</t>
-  </si>
-  <si>
-    <t>ZFPSL</t>
-  </si>
-  <si>
-    <t>需求配送日</t>
-  </si>
-  <si>
-    <t>PSJZRQ</t>
-  </si>
-  <si>
-    <t>短驳计划号</t>
-  </si>
-  <si>
-    <t>DBJH</t>
-  </si>
-  <si>
-    <t>WCT生成</t>
-  </si>
-  <si>
-    <t>成功的话消息“返回短驳计划号”</t>
-  </si>
-  <si>
-    <t>预约信息发送WCT接口</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1066,7 +1124,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1166,6 +1224,32 @@
       <color rgb="FF70AD47"/>
       <name val="Microsoft YaHei"/>
       <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Microsoft YaHei"/>
+      <family val="1"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1282,7 +1366,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1366,6 +1450,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1393,6 +1483,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1417,13 +1510,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>241300</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>82550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1753,12 +1846,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:E12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="38.77734375" style="15" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" style="15" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" style="15" customWidth="1"/>
+    <col min="1" max="1" width="19.625" style="15" customWidth="1"/>
+    <col min="2" max="2" width="38.75" style="15" customWidth="1"/>
+    <col min="3" max="3" width="12.875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="16.25" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:5">
@@ -1853,7 +1946,7 @@
     <row r="10" spans="1:5">
       <c r="A10" s="16"/>
       <c r="B10" s="7" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
@@ -1892,339 +1985,339 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="16.109375" style="15" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="12.21875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="16.125" style="15" customWidth="1"/>
+    <col min="7" max="7" width="14.375" style="15" customWidth="1"/>
+    <col min="8" max="8" width="12.25" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="3" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="16" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="B4" s="16" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="B5" s="16" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="B6" s="16" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="B7" s="16" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="B8" s="16" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="16" customFormat="1">
       <c r="B9" s="16" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="G9" s="39" t="s">
-        <v>320</v>
+        <v>136</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>313</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="16" customFormat="1">
       <c r="B10" s="16" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="G10" s="32"/>
+        <v>147</v>
+      </c>
+      <c r="G10" s="34"/>
       <c r="H10" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="B11" s="7" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="G11" s="31"/>
+        <v>75</v>
+      </c>
+      <c r="G11" s="33"/>
       <c r="H11" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="B12" s="16" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="G12" s="31"/>
+        <v>79</v>
+      </c>
+      <c r="G12" s="33"/>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8" s="16" customFormat="1">
       <c r="B13" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="32"/>
+        <v>64</v>
+      </c>
+      <c r="G13" s="34"/>
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" s="2" customFormat="1">
       <c r="B14" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:8">
       <c r="B15" s="7" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="B16" s="7" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="B17" s="16" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="B18" s="7" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="B19" s="16" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="B20" s="16" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1">
       <c r="B21" s="2" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1">
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1">
       <c r="B23" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1">
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G24" s="6"/>
     </row>
@@ -2234,43 +2327,43 @@
     <row r="26" spans="1:7" s="16" customFormat="1"/>
     <row r="27" spans="1:7">
       <c r="A27" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="B28" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="E28" s="41" t="s">
+        <v>321</v>
+      </c>
+      <c r="F28" s="34"/>
+      <c r="G28" s="33"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="B29" s="33"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="16" t="s">
         <v>127</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="B28" s="36" t="s">
-        <v>131</v>
-      </c>
-      <c r="C28" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="D28" s="37" t="s">
-        <v>133</v>
-      </c>
-      <c r="E28" s="39" t="s">
-        <v>328</v>
-      </c>
-      <c r="F28" s="32"/>
-      <c r="G28" s="31"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="B29" s="31"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="16" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2290,9 +2383,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="2.44140625" style="15" customWidth="1"/>
+    <col min="1" max="1" width="2.5" style="15" customWidth="1"/>
     <col min="2" max="2" width="30" style="15" customWidth="1"/>
     <col min="3" max="3" width="16" style="15" customWidth="1"/>
     <col min="4" max="4" width="38" style="15" customWidth="1"/>
@@ -2305,7 +2398,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:6" ht="16.05" customHeight="1">
+    <row r="2" spans="2:6" ht="16.149999999999999" customHeight="1">
       <c r="B2" s="19" t="s">
         <v>31</v>
       </c>
@@ -2323,169 +2416,170 @@
     </row>
     <row r="5" spans="2:6" ht="66" customHeight="1">
       <c r="B5" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="C5" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="24" t="s">
+    </row>
+    <row r="6" spans="2:6" ht="16.149999999999999" customHeight="1">
+      <c r="D6" s="25" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" ht="16.05" customHeight="1">
-      <c r="D6" s="25" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="66" customHeight="1">
       <c r="D7" s="26" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" ht="16.05" customHeight="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="16.149999999999999" customHeight="1">
       <c r="D8" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="66" customHeight="1">
       <c r="C9" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" ht="16.05" customHeight="1">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="16.149999999999999" customHeight="1">
       <c r="D10" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="66" customHeight="1">
       <c r="C11" s="24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" ht="16.05" customHeight="1">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="16.149999999999999" customHeight="1">
       <c r="D12" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="66" customHeight="1">
       <c r="D13" s="26" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" ht="16.05" customHeight="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="16.149999999999999" customHeight="1">
       <c r="D14" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="66" customHeight="1">
       <c r="D15" s="28" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" ht="16.05" customHeight="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="16.149999999999999" customHeight="1">
       <c r="D16" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="66" customHeight="1">
       <c r="C17" s="24" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" ht="16.05" customHeight="1">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="16.149999999999999" customHeight="1">
       <c r="D18" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="66" customHeight="1">
       <c r="C19" s="24" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" ht="16.05" customHeight="1">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="16.149999999999999" customHeight="1">
       <c r="D20" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="66" customHeight="1">
       <c r="D21" s="27" t="s">
-        <v>49</v>
+        <v>331</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" ht="16.05" customHeight="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" ht="16.149999999999999" customHeight="1">
       <c r="D22" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="66" customHeight="1">
       <c r="E23" s="24" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F23" s="29" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" ht="16.05" customHeight="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" ht="16.149999999999999" customHeight="1">
       <c r="D24" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="66" customHeight="1">
-      <c r="B25" s="23" t="s">
-        <v>53</v>
+      <c r="B25" s="42" t="s">
+        <v>332</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" ht="16.05" customHeight="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" ht="16.149999999999999" customHeight="1">
       <c r="D26" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="2:6" ht="66" customHeight="1">
       <c r="D27" s="26" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" ht="16.05" customHeight="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" ht="16.149999999999999" customHeight="1">
       <c r="D28" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="2:6" ht="66" customHeight="1">
       <c r="C29" s="24" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:H34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="16.21875" style="15" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" style="15" customWidth="1"/>
+    <col min="2" max="2" width="16.25" style="15" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2494,1082 +2588,1102 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
+      <c r="A3" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="16" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="16" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="16" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="10" customFormat="1">
       <c r="B10" s="10" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="5" customFormat="1">
       <c r="B11" s="5" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="10" customFormat="1">
       <c r="B12" s="10" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="B13" s="16" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="B14" s="16" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="B15" s="16" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="B16" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="D18" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="F18" s="16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" s="30" customFormat="1">
+      <c r="B19" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="C20" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="F16" s="16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="B17" s="16" t="s">
+      <c r="D20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" s="16" customFormat="1">
+      <c r="B21" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C21" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="B18" s="16" t="s">
+      <c r="D21" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="16" t="s">
+    </row>
+    <row r="22" spans="2:8" s="10" customFormat="1">
+      <c r="B22" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" s="16" t="s">
+      <c r="C22" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F18" s="16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="B19" s="16" t="s">
+      <c r="D22" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="E22" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D19" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" s="16" customFormat="1">
-      <c r="B20" s="7" t="s">
+      <c r="F22" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C23" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20" s="8" t="s">
+      <c r="D23" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="16" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" s="10" customFormat="1">
-      <c r="B21" s="10" t="s">
+      <c r="F23" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="C21" s="10" t="s">
+    </row>
+    <row r="24" spans="2:8" ht="15.6" customHeight="1">
+      <c r="B24" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="C24" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="D24" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G24" s="34"/>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="F21" s="10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="B22" s="16" t="s">
+      <c r="C25" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="D25" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G25" s="34"/>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="D22" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" s="16" t="s">
+      <c r="C26" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="F22" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G22" s="33" t="s">
+      <c r="D26" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="16" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="15.6" customHeight="1">
-      <c r="B23" s="16" t="s">
+      <c r="F26" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G26" s="34"/>
+    </row>
+    <row r="27" spans="2:8" s="10" customFormat="1">
+      <c r="B27" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C27" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="D23" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" s="32"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="B24" s="16" t="s">
+      <c r="D27" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" s="10" customFormat="1">
+      <c r="B28" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C28" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D24" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="32"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="B25" s="16" t="s">
+      <c r="D28" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C29" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D25" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E25" s="16" t="s">
+      <c r="D29" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="F25" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G25" s="32"/>
-    </row>
-    <row r="26" spans="1:8" s="10" customFormat="1">
-      <c r="B26" s="10" t="s">
+      <c r="F29" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" s="10" customFormat="1">
+      <c r="B30" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C30" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="D26" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" s="10" customFormat="1">
-      <c r="B27" s="10" t="s">
+      <c r="D30" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G30" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="4" t="s">
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="D27" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="B28" s="16" t="s">
+      <c r="C31" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="D31" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E31" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E28" s="7" t="s">
+      <c r="F31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="F28" s="16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" s="10" customFormat="1">
-      <c r="B29" s="10" t="s">
+      <c r="H31" s="16"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="B33" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D29" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="G29" s="10" t="s">
+      <c r="C33" s="16" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="B30" s="7" t="s">
+      <c r="D33" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="E33" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="D30" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="E30" s="7" t="s">
+    </row>
+    <row r="34" spans="1:5">
+      <c r="B34" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="F30" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G30" s="8" t="s">
+      <c r="C34" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="H30" s="16"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="16" t="s">
+      <c r="D34" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="E34" s="16" t="s">
         <v>127</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="G22:G25"/>
+    <mergeCell ref="G23:G26"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N48"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="16.21875" style="15" customWidth="1"/>
-    <col min="6" max="6" width="32.88671875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="16.25" style="15" customWidth="1"/>
+    <col min="6" max="6" width="32.875" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="16" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="16" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="B4" s="16" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" s="16" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="16" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1">
       <c r="B10" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="B11" s="16" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1">
       <c r="B12" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="B13" s="16" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1">
       <c r="B14" s="2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1">
       <c r="B15" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1">
       <c r="B16" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="2:6" s="2" customFormat="1">
       <c r="B17" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="2:6" s="2" customFormat="1">
       <c r="B18" s="2" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="2:6" s="2" customFormat="1">
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="16" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="2:6" s="2" customFormat="1">
       <c r="B21" s="2" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="2:6" s="2" customFormat="1">
       <c r="B22" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F22" s="30" t="s">
-        <v>161</v>
+        <v>64</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="2:6" s="2" customFormat="1">
       <c r="B23" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F23" s="34"/>
+        <v>157</v>
+      </c>
+      <c r="F23" s="36"/>
     </row>
     <row r="24" spans="2:6" s="2" customFormat="1">
       <c r="B24" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F24" s="34"/>
+        <v>136</v>
+      </c>
+      <c r="F24" s="36"/>
     </row>
     <row r="25" spans="2:6" s="2" customFormat="1">
       <c r="B25" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F25" s="34"/>
+        <v>57</v>
+      </c>
+      <c r="F25" s="36"/>
     </row>
     <row r="26" spans="2:6" s="2" customFormat="1">
       <c r="B26" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F26" s="34"/>
+        <v>57</v>
+      </c>
+      <c r="F26" s="36"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="7" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="F27" s="31"/>
+        <v>166</v>
+      </c>
+      <c r="F27" s="33"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="7" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="F28" s="31"/>
+        <v>169</v>
+      </c>
+      <c r="F28" s="33"/>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="16" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="F29" s="31"/>
+        <v>117</v>
+      </c>
+      <c r="F29" s="33"/>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="16" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="F30" s="31"/>
+        <v>175</v>
+      </c>
+      <c r="F30" s="33"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="16" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="F31" s="31"/>
+        <v>117</v>
+      </c>
+      <c r="F31" s="33"/>
     </row>
     <row r="32" spans="2:6">
       <c r="F32" s="14"/>
     </row>
     <row r="33" spans="2:14">
       <c r="B33" s="10" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="2:14">
       <c r="B34" s="10" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="2:14" ht="36" customHeight="1">
       <c r="B36" s="16" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="G36" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="32"/>
-      <c r="N36" s="32"/>
+        <v>184</v>
+      </c>
+      <c r="G36" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="H36" s="34"/>
+      <c r="I36" s="34"/>
+      <c r="J36" s="34"/>
+      <c r="K36" s="34"/>
+      <c r="L36" s="34"/>
+      <c r="M36" s="34"/>
+      <c r="N36" s="34"/>
     </row>
     <row r="37" spans="2:14">
       <c r="B37" s="16" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="G37" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="H37" s="32"/>
-      <c r="I37" s="32"/>
-      <c r="J37" s="32"/>
-      <c r="K37" s="32"/>
-      <c r="L37" s="32"/>
-      <c r="M37" s="32"/>
-      <c r="N37" s="32"/>
+        <v>188</v>
+      </c>
+      <c r="G37" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="H37" s="34"/>
+      <c r="I37" s="34"/>
+      <c r="J37" s="34"/>
+      <c r="K37" s="34"/>
+      <c r="L37" s="34"/>
+      <c r="M37" s="34"/>
+      <c r="N37" s="34"/>
     </row>
     <row r="39" spans="2:14">
       <c r="B39" s="16" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="2:14">
-      <c r="B40" s="35" t="s">
-        <v>198</v>
-      </c>
-      <c r="C40" s="32"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="32"/>
-      <c r="J40" s="32"/>
-      <c r="K40" s="32"/>
-      <c r="L40" s="32"/>
-      <c r="M40" s="32"/>
+      <c r="B40" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="34"/>
+      <c r="I40" s="34"/>
+      <c r="J40" s="34"/>
+      <c r="K40" s="34"/>
+      <c r="L40" s="34"/>
+      <c r="M40" s="34"/>
     </row>
     <row r="41" spans="2:14">
-      <c r="B41" s="31"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="32"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="32"/>
-      <c r="L41" s="32"/>
-      <c r="M41" s="32"/>
+      <c r="B41" s="33"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="34"/>
+      <c r="I41" s="34"/>
+      <c r="J41" s="34"/>
+      <c r="K41" s="34"/>
+      <c r="L41" s="34"/>
+      <c r="M41" s="34"/>
     </row>
     <row r="42" spans="2:14">
-      <c r="B42" s="31"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="32"/>
-      <c r="J42" s="32"/>
-      <c r="K42" s="32"/>
-      <c r="L42" s="32"/>
-      <c r="M42" s="32"/>
+      <c r="B42" s="33"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="34"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="34"/>
+      <c r="K42" s="34"/>
+      <c r="L42" s="34"/>
+      <c r="M42" s="34"/>
     </row>
     <row r="43" spans="2:14">
-      <c r="B43" s="31"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32"/>
-      <c r="J43" s="32"/>
-      <c r="K43" s="32"/>
-      <c r="L43" s="32"/>
-      <c r="M43" s="32"/>
+      <c r="B43" s="33"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="34"/>
+      <c r="L43" s="34"/>
+      <c r="M43" s="34"/>
     </row>
     <row r="44" spans="2:14">
-      <c r="B44" s="31"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="32"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="32"/>
-      <c r="J44" s="32"/>
-      <c r="K44" s="32"/>
-      <c r="L44" s="32"/>
-      <c r="M44" s="32"/>
+      <c r="B44" s="33"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="33"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
+      <c r="J44" s="34"/>
+      <c r="K44" s="34"/>
+      <c r="L44" s="34"/>
+      <c r="M44" s="34"/>
     </row>
     <row r="45" spans="2:14">
-      <c r="B45" s="31"/>
-      <c r="C45" s="32"/>
-      <c r="D45" s="32"/>
-      <c r="E45" s="32"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
-      <c r="I45" s="32"/>
-      <c r="J45" s="32"/>
-      <c r="K45" s="32"/>
-      <c r="L45" s="32"/>
-      <c r="M45" s="32"/>
+      <c r="B45" s="33"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="33"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="34"/>
+      <c r="I45" s="34"/>
+      <c r="J45" s="34"/>
+      <c r="K45" s="34"/>
+      <c r="L45" s="34"/>
+      <c r="M45" s="34"/>
     </row>
     <row r="46" spans="2:14">
-      <c r="B46" s="31"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
-      <c r="E46" s="32"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32"/>
-      <c r="I46" s="32"/>
-      <c r="J46" s="32"/>
-      <c r="K46" s="32"/>
-      <c r="L46" s="32"/>
-      <c r="M46" s="32"/>
+      <c r="B46" s="33"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="34"/>
+      <c r="H46" s="34"/>
+      <c r="I46" s="34"/>
+      <c r="J46" s="34"/>
+      <c r="K46" s="34"/>
+      <c r="L46" s="34"/>
+      <c r="M46" s="34"/>
     </row>
     <row r="47" spans="2:14">
-      <c r="B47" s="31"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="32"/>
-      <c r="K47" s="32"/>
-      <c r="L47" s="32"/>
-      <c r="M47" s="32"/>
+      <c r="B47" s="33"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="33"/>
+      <c r="G47" s="34"/>
+      <c r="H47" s="34"/>
+      <c r="I47" s="34"/>
+      <c r="J47" s="34"/>
+      <c r="K47" s="34"/>
+      <c r="L47" s="34"/>
+      <c r="M47" s="34"/>
     </row>
     <row r="48" spans="2:14">
-      <c r="B48" s="31"/>
-      <c r="C48" s="32"/>
-      <c r="D48" s="32"/>
-      <c r="E48" s="32"/>
-      <c r="F48" s="31"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="32"/>
-      <c r="I48" s="32"/>
-      <c r="J48" s="32"/>
-      <c r="K48" s="32"/>
-      <c r="L48" s="32"/>
-      <c r="M48" s="32"/>
+      <c r="B48" s="33"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="34"/>
+      <c r="F48" s="33"/>
+      <c r="G48" s="34"/>
+      <c r="H48" s="34"/>
+      <c r="I48" s="34"/>
+      <c r="J48" s="34"/>
+      <c r="K48" s="34"/>
+      <c r="L48" s="34"/>
+      <c r="M48" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3587,72 +3701,72 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F63"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="18.44140625" style="15" customWidth="1"/>
-    <col min="6" max="6" width="21.88671875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="15" customWidth="1"/>
+    <col min="6" max="6" width="21.875" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="16" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="16" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="16" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" s="16" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" s="16" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="16" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="B10" s="16" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D10" s="16">
         <v>10</v>
@@ -3661,15 +3775,15 @@
         <v>0</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="B11" s="16" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D11" s="16">
         <v>10</v>
@@ -3678,15 +3792,15 @@
         <v>0</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="B12" s="16" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D12" s="16">
         <v>6</v>
@@ -3695,15 +3809,15 @@
         <v>0</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="B13" s="16" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D13" s="16">
         <v>4</v>
@@ -3712,15 +3826,15 @@
         <v>0</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="B14" s="16" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D14" s="16">
         <v>4</v>
@@ -3729,15 +3843,15 @@
         <v>0</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="B15" s="16" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D15" s="16">
         <v>1</v>
@@ -3746,15 +3860,15 @@
         <v>0</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="B16" s="16" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D16" s="16">
         <v>10</v>
@@ -3763,15 +3877,15 @@
         <v>0</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="2:6">
       <c r="B17" s="16" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D17" s="16">
         <v>5</v>
@@ -3780,15 +3894,15 @@
         <v>0</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="16" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D18" s="16">
         <v>4</v>
@@ -3797,15 +3911,15 @@
         <v>0</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" s="16" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D19" s="16">
         <v>18</v>
@@ -3814,15 +3928,15 @@
         <v>0</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="16" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D20" s="16">
         <v>18</v>
@@ -3831,15 +3945,15 @@
         <v>0</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="16" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D21" s="16">
         <v>10</v>
@@ -3848,15 +3962,15 @@
         <v>0</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="16" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D22" s="16">
         <v>20</v>
@@ -3865,15 +3979,15 @@
         <v>0</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="16" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D23" s="16">
         <v>4</v>
@@ -3882,15 +3996,15 @@
         <v>0</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="16" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D24" s="16">
         <v>4</v>
@@ -3899,15 +4013,15 @@
         <v>0</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="16" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D25" s="16">
         <v>1</v>
@@ -3916,15 +4030,15 @@
         <v>0</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="16" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D26" s="16">
         <v>3</v>
@@ -3933,15 +4047,15 @@
         <v>0</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="16" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D27" s="16">
         <v>13</v>
@@ -3950,15 +4064,15 @@
         <v>3</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="16" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D28" s="16">
         <v>3</v>
@@ -3967,15 +4081,15 @@
         <v>0</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="16" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D29" s="16">
         <v>13</v>
@@ -3984,15 +4098,15 @@
         <v>3</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="16" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D30" s="16">
         <v>13</v>
@@ -4001,15 +4115,15 @@
         <v>3</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="16" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D31" s="16">
         <v>10</v>
@@ -4018,15 +4132,15 @@
         <v>0</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="16" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D32" s="16">
         <v>13</v>
@@ -4035,15 +4149,15 @@
         <v>3</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="16" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D33" s="16">
         <v>13</v>
@@ -4052,15 +4166,15 @@
         <v>3</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="16" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D34" s="16">
         <v>13</v>
@@ -4069,15 +4183,15 @@
         <v>3</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="16" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D35" s="16">
         <v>13</v>
@@ -4086,15 +4200,15 @@
         <v>3</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36" spans="2:6">
       <c r="B36" s="16" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D36" s="16">
         <v>8</v>
@@ -4103,15 +4217,15 @@
         <v>0</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="16" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D37" s="16">
         <v>4</v>
@@ -4120,15 +4234,15 @@
         <v>0</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
     </row>
     <row r="38" spans="2:6" s="2" customFormat="1">
       <c r="B38" s="2" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D38" s="2">
         <v>8</v>
@@ -4137,15 +4251,15 @@
         <v>0</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="16" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D39" s="16">
         <v>8</v>
@@ -4154,15 +4268,15 @@
         <v>0</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="16" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D40" s="16">
         <v>8</v>
@@ -4171,15 +4285,15 @@
         <v>0</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="16" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D41" s="16">
         <v>30</v>
@@ -4188,15 +4302,15 @@
         <v>0</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="16" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D42" s="16">
         <v>30</v>
@@ -4205,15 +4319,15 @@
         <v>0</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="16" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D43" s="16">
         <v>25</v>
@@ -4222,15 +4336,15 @@
         <v>0</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="16" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D44" s="16">
         <v>40</v>
@@ -4239,15 +4353,15 @@
         <v>0</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="16" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D45" s="16">
         <v>50</v>
@@ -4256,15 +4370,15 @@
         <v>0</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="16" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D46" s="16">
         <v>50</v>
@@ -4273,15 +4387,15 @@
         <v>0</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
     </row>
     <row r="47" spans="2:6">
       <c r="B47" s="16" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D47" s="16">
         <v>16</v>
@@ -4290,15 +4404,15 @@
         <v>0</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="16" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D48" s="16">
         <v>60</v>
@@ -4307,15 +4421,15 @@
         <v>0</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="16" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D49" s="16">
         <v>20</v>
@@ -4324,15 +4438,15 @@
         <v>0</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="16" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D50" s="16">
         <v>20</v>
@@ -4341,15 +4455,15 @@
         <v>0</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="16" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D51" s="16">
         <v>20</v>
@@ -4358,15 +4472,15 @@
         <v>0</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="16" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D52" s="16">
         <v>13</v>
@@ -4375,15 +4489,15 @@
         <v>3</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="16" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D53" s="16">
         <v>3</v>
@@ -4392,15 +4506,15 @@
         <v>0</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="16" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="D54" s="16">
         <v>0</v>
@@ -4409,15 +4523,15 @@
         <v>0</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="16" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D55" s="16">
         <v>12</v>
@@ -4426,15 +4540,15 @@
         <v>0</v>
       </c>
       <c r="F55" s="16" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="16" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D56" s="16">
         <v>8</v>
@@ -4443,15 +4557,15 @@
         <v>0</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="16" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D57" s="16">
         <v>6</v>
@@ -4460,15 +4574,15 @@
         <v>0</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="16" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D58" s="16">
         <v>12</v>
@@ -4477,15 +4591,15 @@
         <v>0</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="16" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D59" s="16">
         <v>8</v>
@@ -4494,15 +4608,15 @@
         <v>0</v>
       </c>
       <c r="F59" s="16" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="16" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D60" s="16">
         <v>6</v>
@@ -4511,15 +4625,15 @@
         <v>0</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="16" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D61" s="16">
         <v>1</v>
@@ -4528,15 +4642,15 @@
         <v>0</v>
       </c>
       <c r="F61" s="16" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="16" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D62" s="16">
         <v>1</v>
@@ -4545,15 +4659,15 @@
         <v>0</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="16" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D63" s="16">
         <v>13</v>
@@ -4562,7 +4676,7 @@
         <v>9</v>
       </c>
       <c r="F63" s="16" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -4574,11 +4688,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="16" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -4590,7 +4704,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:O24"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="14" style="15" customWidth="1"/>
   </cols>
@@ -4602,330 +4716,330 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="16" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="B4" s="16" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="B5" s="16" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="B6" s="16" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="B7" s="16" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="B8" s="16" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="B9" s="16" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="B10" s="16" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="B11" s="16" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="B12" s="16" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="B13" s="16" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="B14" s="16" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="B15" s="16" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="J15" s="35" t="s">
-        <v>304</v>
-      </c>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="32"/>
-      <c r="O15" s="32"/>
+        <v>79</v>
+      </c>
+      <c r="J15" s="37" t="s">
+        <v>297</v>
+      </c>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
     </row>
     <row r="16" spans="1:15">
       <c r="B16" s="16" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="32"/>
-      <c r="O16" s="32"/>
+        <v>136</v>
+      </c>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
     </row>
     <row r="17" spans="1:15">
       <c r="B17" s="16" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32"/>
-      <c r="O17" s="32"/>
+        <v>75</v>
+      </c>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
     </row>
     <row r="18" spans="1:15">
       <c r="B18" s="16" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="32"/>
-      <c r="O18" s="32"/>
+        <v>79</v>
+      </c>
+      <c r="J18" s="34"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="34"/>
+      <c r="M18" s="34"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="34"/>
     </row>
     <row r="19" spans="1:15">
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="32"/>
-      <c r="N19" s="32"/>
-      <c r="O19" s="32"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="34"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="34"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
-      <c r="M20" s="32"/>
-      <c r="N20" s="32"/>
-      <c r="O20" s="32"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="34"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="32"/>
-      <c r="O21" s="32"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+    </row>
+    <row r="23" spans="1:15" ht="34.9" customHeight="1">
+      <c r="B23" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="E23" s="40" t="s">
+        <v>300</v>
+      </c>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="34"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="B24" s="33"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="C22" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="32"/>
-      <c r="O22" s="32"/>
-    </row>
-    <row r="23" spans="1:15" ht="34.950000000000003" customHeight="1">
-      <c r="B23" s="36" t="s">
-        <v>131</v>
-      </c>
-      <c r="C23" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="D23" s="37" t="s">
-        <v>133</v>
-      </c>
-      <c r="E23" s="38" t="s">
-        <v>307</v>
-      </c>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="32"/>
-      <c r="O23" s="32"/>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="B24" s="31"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32"/>
-      <c r="M24" s="32"/>
-      <c r="N24" s="32"/>
-      <c r="O24" s="32"/>
+      <c r="J24" s="34"/>
+      <c r="K24" s="34"/>
+      <c r="L24" s="34"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="34"/>
+      <c r="O24" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4944,147 +5058,147 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="16" customWidth="1"/>
+    <col min="1" max="1" width="8.75" style="16" customWidth="1"/>
     <col min="2" max="2" width="14" style="16" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375" style="16" customWidth="1"/>
-    <col min="4" max="16384" width="8.77734375" style="16"/>
+    <col min="3" max="3" width="8.75" style="16" customWidth="1"/>
+    <col min="4" max="16384" width="8.75" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="16" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="16" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="B4" s="16" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="B5" s="16" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="G5" s="35" t="s">
-        <v>312</v>
-      </c>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
+        <v>136</v>
+      </c>
+      <c r="G5" s="37" t="s">
+        <v>305</v>
+      </c>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
     </row>
     <row r="6" spans="1:11">
       <c r="B6" s="16" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
+        <v>68</v>
+      </c>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
     </row>
     <row r="7" spans="1:11">
       <c r="B7" s="16" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
+        <v>136</v>
+      </c>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
     </row>
     <row r="8" spans="1:11">
       <c r="B8" s="16" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
+        <v>136</v>
+      </c>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
     </row>
     <row r="9" spans="1:11">
       <c r="B9" s="16" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
+        <v>157</v>
+      </c>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="16" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C11" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E11" s="16">
         <v>1</v>
@@ -5092,13 +5206,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="B12" s="16" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E12" s="16">
         <v>220</v>
@@ -5116,10 +5230,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="16" customWidth="1"/>
-    <col min="2" max="16384" width="8.77734375" style="16"/>
+    <col min="1" max="1" width="8.75" style="16" customWidth="1"/>
+    <col min="2" max="16384" width="8.75" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5129,29 +5243,29 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="16" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="16" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="16" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E7" s="16">
         <v>1</v>
@@ -5159,13 +5273,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="16" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E8" s="16">
         <v>220</v>

--- a/aspnet-core/prototype/领用配送接口FS(2).xlsx
+++ b/aspnet-core/prototype/领用配送接口FS(2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\module-zero-core-template\aspnet-core\prototype\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE41C552-4E96-4FB4-A988-724B30EF8593}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB205291-D54E-4041-9780-6D51ECB5815E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6945" tabRatio="669" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6948" tabRatio="669" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="目录" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="A-LM-ABAP-WMZC588" sheetId="3" r:id="rId3"/>
     <sheet name="A-LM-ABAP-WMZC591" sheetId="4" r:id="rId4"/>
     <sheet name="A-LM-ABAP-WMZC592" sheetId="5" r:id="rId5"/>
-    <sheet name="A-LM-ABAP-WMZC594" sheetId="7" r:id="rId6"/>
-    <sheet name="A-LM-ABAP-WMZC593" sheetId="6" r:id="rId7"/>
+    <sheet name="A-LM-ABAP-WMZC593" sheetId="6" r:id="rId6"/>
+    <sheet name="A-LM-ABAP-WMZC594" sheetId="7" r:id="rId7"/>
     <sheet name="A-LM-ABAP-WMZC633" sheetId="8" r:id="rId8"/>
     <sheet name="A-LM-ABAP-WMZC638" sheetId="9" r:id="rId9"/>
     <sheet name="A-LM-ABAP-WMZC666" sheetId="10" r:id="rId10"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="355">
   <si>
     <t>A-LM-ABAP-WMZC588</t>
   </si>
@@ -930,9 +930,6 @@
     <t>配送需求单行</t>
   </si>
   <si>
-    <t>PSXQH</t>
-  </si>
-  <si>
     <t>备注：可能没有，字段保留，可以为空</t>
   </si>
   <si>
@@ -950,9 +947,6 @@
     <t>ZJPSL</t>
   </si>
   <si>
-    <t>成功的话消息“配送需求&amp;行XX，拣配单&amp;行XX已生成”</t>
-  </si>
-  <si>
     <t>配送计划完成，过账接口</t>
   </si>
   <si>
@@ -982,9 +976,6 @@
   </si>
   <si>
     <t>LM-INT-037接口接收到ATMS预约信息之后，ZLMT04660表中启用控制塔的工厂的数据触发此接口发送给WCT</t>
-  </si>
-  <si>
-    <t>同链接输出内容</t>
   </si>
   <si>
     <t>短驳计划接口，WCT发送ATMS</t>
@@ -1119,12 +1110,135 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>ZPSXQ</t>
+  </si>
+  <si>
+    <t>ZPSXQH</t>
+  </si>
+  <si>
+    <t>实际发货数量</t>
+  </si>
+  <si>
+    <t>JPSL</t>
+  </si>
+  <si>
+    <t>20260720新增</t>
+  </si>
+  <si>
+    <t>领料单</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">1 WCT任务完成确认后，触发接口
+2 根据输入的信息，在ZLMT00307里查找相应的拣配单及行项目，模拟ZLM00354的领料拣配过账
+3 过账成功后，MESSAGE typeS，以及详细字段信息，如果失败为E，返回具体报错消息
+4 如果多行数据，分多段输出
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5 WCT结束任务时用户会输入实际任务数量，根据WCT将此数量作为实际发货数量，SAP接收数据后修改ZLMT00307-JPSL，作为发货过账数量，再处理过账</t>
+    </r>
+  </si>
+  <si>
+    <t>拣配单行项目</t>
+  </si>
+  <si>
+    <t>物料凭证号</t>
+  </si>
+  <si>
+    <t>MBLNR</t>
+  </si>
+  <si>
+    <t>物料凭证年度</t>
+  </si>
+  <si>
+    <t>MJAHR</t>
+  </si>
+  <si>
+    <t>物料凭证行项目</t>
+  </si>
+  <si>
+    <t>ZEILE</t>
+  </si>
+  <si>
+    <t>转储单编号</t>
+  </si>
+  <si>
+    <t>TANUM</t>
+  </si>
+  <si>
+    <t>转储单项目</t>
+  </si>
+  <si>
+    <t>TAPOS</t>
+  </si>
+  <si>
+    <t>重复下发不接收数据</t>
+  </si>
+  <si>
+    <t>成功的话返回以下字段</t>
+  </si>
+  <si>
+    <t>如果多行数据分多段输出</t>
+  </si>
+  <si>
+    <t>拣配单</t>
+  </si>
+  <si>
+    <t>拣配行</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF800080"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>同链接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF800080"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>输出内容</t>
+    </r>
+  </si>
+  <si>
+    <t>LM-INT-WCT-071</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1252,6 +1366,29 @@
       <family val="1"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -1366,7 +1503,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1388,9 +1525,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1455,6 +1589,9 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1477,14 +1614,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1846,19 +2028,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:E12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="19.625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="38.75" style="15" customWidth="1"/>
-    <col min="3" max="3" width="12.875" style="15" customWidth="1"/>
-    <col min="4" max="4" width="16.25" style="15" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="38.77734375" style="14" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:5">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="7" t="s">
@@ -1866,43 +2048,43 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="15" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="15" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="7" t="s">
@@ -1910,7 +2092,7 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1921,54 +2103,57 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>18</v>
       </c>
+      <c r="D8" s="7" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="9"/>
       <c r="D9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="16"/>
+      <c r="A10" s="15"/>
       <c r="B10" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
+        <v>319</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>24</v>
       </c>
       <c r="B11" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="16"/>
+      <c r="C11" s="15"/>
       <c r="D11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="15" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="12" t="s">
         <v>28</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -1985,121 +2170,121 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="16.125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="14.375" style="15" customWidth="1"/>
-    <col min="8" max="8" width="12.25" style="15" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" style="14" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" style="14" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="15" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="16" t="s">
+      <c r="D4" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>291</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="16" t="s">
+      <c r="D5" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="16" t="s">
+      <c r="D6" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="15" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" s="16" customFormat="1">
-      <c r="B9" s="16" t="s">
+      <c r="D8" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="15" customFormat="1">
+      <c r="B9" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="16" t="s">
+      <c r="D9" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="G9" s="41" t="s">
-        <v>313</v>
+      <c r="G9" s="40" t="s">
+        <v>310</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="16" customFormat="1">
-      <c r="B10" s="16" t="s">
+    <row r="10" spans="1:8" s="15" customFormat="1">
+      <c r="B10" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="15" t="s">
         <v>56</v>
       </c>
       <c r="E10" s="7" t="s">
@@ -2112,15 +2297,15 @@
     </row>
     <row r="11" spans="1:8">
       <c r="B11" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="D11" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="D11" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G11" s="33"/>
@@ -2129,22 +2314,22 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="15" t="s">
         <v>79</v>
       </c>
       <c r="G12" s="33"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" s="16" customFormat="1">
+    <row r="13" spans="1:8" s="15" customFormat="1">
       <c r="B13" s="2" t="s">
         <v>152</v>
       </c>
@@ -2204,67 +2389,67 @@
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="D17" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="16" t="s">
+      <c r="D17" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="15" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="B18" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="C18" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="15" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="D19" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="16" t="s">
+      <c r="D19" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="15" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="15" t="s">
         <v>100</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D20" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="D20" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="15" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1">
       <c r="B21" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>56</v>
@@ -2273,7 +2458,7 @@
         <v>136</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1">
@@ -2324,21 +2509,21 @@
     <row r="25" spans="1:7" s="2" customFormat="1">
       <c r="G25" s="6"/>
     </row>
-    <row r="26" spans="1:7" s="16" customFormat="1"/>
+    <row r="26" spans="1:7" s="15" customFormat="1"/>
     <row r="27" spans="1:7">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="E27" s="16" t="s">
+      <c r="E27" s="15" t="s">
         <v>123</v>
       </c>
     </row>
@@ -2352,8 +2537,8 @@
       <c r="D28" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="E28" s="41" t="s">
-        <v>321</v>
+      <c r="E28" s="40" t="s">
+        <v>318</v>
       </c>
       <c r="F28" s="34"/>
       <c r="G28" s="33"/>
@@ -2362,7 +2547,7 @@
       <c r="B29" s="33"/>
       <c r="C29" s="34"/>
       <c r="D29" s="34"/>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="15" t="s">
         <v>127</v>
       </c>
     </row>
@@ -2383,186 +2568,186 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.5" style="15" customWidth="1"/>
-    <col min="2" max="2" width="30" style="15" customWidth="1"/>
-    <col min="3" max="3" width="16" style="15" customWidth="1"/>
-    <col min="4" max="4" width="38" style="15" customWidth="1"/>
-    <col min="5" max="5" width="16" style="15" customWidth="1"/>
-    <col min="6" max="6" width="30" style="15" customWidth="1"/>
+    <col min="1" max="1" width="2.44140625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="30" style="14" customWidth="1"/>
+    <col min="3" max="3" width="16" style="14" customWidth="1"/>
+    <col min="4" max="4" width="38" style="14" customWidth="1"/>
+    <col min="5" max="5" width="16" style="14" customWidth="1"/>
+    <col min="6" max="6" width="30" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="30" customHeight="1">
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="17" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:6" ht="16.149999999999999" customHeight="1">
-      <c r="B2" s="19" t="s">
+    <row r="2" spans="2:6" ht="16.2" customHeight="1">
+      <c r="B2" s="18" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="24" customHeight="1">
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="21" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="66" customHeight="1">
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="22" t="s">
+        <v>323</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="16.2" customHeight="1">
+      <c r="D6" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="66" customHeight="1">
+      <c r="D7" s="25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="16.2" customHeight="1">
+      <c r="D8" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="66" customHeight="1">
+      <c r="C9" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="16.2" customHeight="1">
+      <c r="D10" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="66" customHeight="1">
+      <c r="C11" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="16.2" customHeight="1">
+      <c r="D12" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="66" customHeight="1">
+      <c r="D13" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="16.2" customHeight="1">
+      <c r="D14" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="66" customHeight="1">
+      <c r="D15" s="27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="16.2" customHeight="1">
+      <c r="D16" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="66" customHeight="1">
+      <c r="C17" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="26" t="s">
         <v>326</v>
       </c>
-      <c r="C5" s="24" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" ht="16.149999999999999" customHeight="1">
-      <c r="D6" s="25" t="s">
+    </row>
+    <row r="18" spans="2:6" ht="16.2" customHeight="1">
+      <c r="D18" s="24" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="66" customHeight="1">
-      <c r="D7" s="26" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" ht="16.149999999999999" customHeight="1">
-      <c r="D8" s="25" t="s">
+    <row r="19" spans="2:6" ht="66" customHeight="1">
+      <c r="C19" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="16.2" customHeight="1">
+      <c r="D20" s="24" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="66" customHeight="1">
-      <c r="C9" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" ht="16.149999999999999" customHeight="1">
-      <c r="D10" s="25" t="s">
+    <row r="21" spans="2:6" ht="66" customHeight="1">
+      <c r="D21" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" ht="16.2" customHeight="1">
+      <c r="D22" s="24" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="66" customHeight="1">
-      <c r="C11" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" ht="16.149999999999999" customHeight="1">
-      <c r="D12" s="25" t="s">
+    <row r="23" spans="2:6" ht="66" customHeight="1">
+      <c r="E23" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" ht="16.2" customHeight="1">
+      <c r="D24" s="24" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="66" customHeight="1">
-      <c r="D13" s="26" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" ht="16.149999999999999" customHeight="1">
-      <c r="D14" s="25" t="s">
+    <row r="25" spans="2:6" ht="66" customHeight="1">
+      <c r="B25" s="31" t="s">
+        <v>329</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" ht="16.2" customHeight="1">
+      <c r="D26" s="24" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="66" customHeight="1">
-      <c r="D15" s="28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" ht="16.149999999999999" customHeight="1">
-      <c r="D16" s="25" t="s">
+    <row r="27" spans="2:6" ht="66" customHeight="1">
+      <c r="D27" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" ht="16.2" customHeight="1">
+      <c r="D28" s="24" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="66" customHeight="1">
-      <c r="C17" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" ht="16.149999999999999" customHeight="1">
-      <c r="D18" s="25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" ht="66" customHeight="1">
-      <c r="C19" s="24" t="s">
+    <row r="29" spans="2:6" ht="66" customHeight="1">
+      <c r="C29" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="27" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" ht="16.149999999999999" customHeight="1">
-      <c r="D20" s="25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" ht="66" customHeight="1">
-      <c r="D21" s="27" t="s">
-        <v>331</v>
-      </c>
-      <c r="E21" s="24" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" ht="16.149999999999999" customHeight="1">
-      <c r="D22" s="25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" ht="66" customHeight="1">
-      <c r="E23" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="F23" s="29" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" ht="16.149999999999999" customHeight="1">
-      <c r="D24" s="25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" ht="66" customHeight="1">
-      <c r="B25" s="42" t="s">
-        <v>332</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" ht="16.149999999999999" customHeight="1">
-      <c r="D26" s="25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" ht="66" customHeight="1">
-      <c r="D27" s="26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" ht="16.149999999999999" customHeight="1">
-      <c r="D28" s="25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" ht="66" customHeight="1">
-      <c r="C29" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="27" t="s">
+      <c r="D29" s="26" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2576,14 +2761,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="16.25" style="15" customWidth="1"/>
-    <col min="6" max="6" width="10.625" style="15" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" style="14" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2600,34 +2785,34 @@
       <c r="H3" s="34"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="15" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="15" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="15" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="10" customFormat="1">
-      <c r="B10" s="10" t="s">
+    <row r="10" spans="1:8" s="9" customFormat="1">
+      <c r="B10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="10" t="s">
+      <c r="D10" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="9" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2648,163 +2833,163 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="10" customFormat="1">
-      <c r="B12" s="10" t="s">
+    <row r="12" spans="1:8" s="9" customFormat="1">
+      <c r="B12" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="10" t="s">
+      <c r="D12" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="15" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D14" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="16" t="s">
+      <c r="D14" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="15" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="15" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="15" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="17" spans="2:8">
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="16" t="s">
+      <c r="D17" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="15" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="18" spans="2:8">
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="16" t="s">
+      <c r="D18" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="15" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="2:8" s="30" customFormat="1">
+    <row r="19" spans="2:8" s="29" customFormat="1">
       <c r="B19" s="7" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="D19" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="F19" s="30" t="s">
+      <c r="F19" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="G19" s="31" t="s">
-        <v>325</v>
+      <c r="G19" s="30" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="20" spans="2:8">
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="16" t="s">
+      <c r="D20" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="15" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="2:8" s="16" customFormat="1">
+    <row r="21" spans="2:8" s="15" customFormat="1">
       <c r="B21" s="7" t="s">
         <v>87</v>
       </c>
@@ -2814,47 +2999,47 @@
       <c r="D21" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="F21" s="15" t="s">
         <v>61</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="2:8" s="10" customFormat="1">
-      <c r="B22" s="10" t="s">
+    <row r="22" spans="2:8" s="9" customFormat="1">
+      <c r="B22" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="23" spans="2:8">
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="D23" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" s="16" t="s">
+      <c r="D23" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="F23" s="16" t="s">
+      <c r="F23" s="15" t="s">
         <v>61</v>
       </c>
       <c r="G23" s="35" t="s">
@@ -2862,84 +3047,84 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15.6" customHeight="1">
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="15" t="s">
         <v>98</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E24" s="16" t="s">
+      <c r="D24" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="15" t="s">
         <v>61</v>
       </c>
       <c r="G24" s="34"/>
     </row>
     <row r="25" spans="2:8">
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E25" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="F25" s="16" t="s">
+      <c r="F25" s="15" t="s">
         <v>61</v>
       </c>
       <c r="G25" s="34"/>
     </row>
     <row r="26" spans="2:8">
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="D26" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E26" s="16" t="s">
+      <c r="D26" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="16" t="s">
+      <c r="F26" s="15" t="s">
         <v>61</v>
       </c>
       <c r="G26" s="34"/>
     </row>
-    <row r="27" spans="2:8" s="10" customFormat="1">
-      <c r="B27" s="10" t="s">
+    <row r="27" spans="2:8" s="9" customFormat="1">
+      <c r="B27" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="2:8" s="10" customFormat="1">
-      <c r="B28" s="10" t="s">
+    <row r="28" spans="2:8" s="9" customFormat="1">
+      <c r="B28" s="9" t="s">
         <v>107</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="9" t="s">
         <v>56</v>
       </c>
       <c r="E28" s="4" t="s">
@@ -2947,7 +3132,7 @@
       </c>
     </row>
     <row r="29" spans="2:8">
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="15" t="s">
         <v>109</v>
       </c>
       <c r="C29" s="7" t="s">
@@ -2959,27 +3144,27 @@
       <c r="E29" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="F29" s="16" t="s">
+      <c r="F29" s="15" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="2:8" s="10" customFormat="1">
-      <c r="B30" s="10" t="s">
+    <row r="30" spans="2:8" s="9" customFormat="1">
+      <c r="B30" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D30" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E30" s="10" t="s">
+      <c r="D30" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G30" s="9" t="s">
         <v>114</v>
       </c>
     </row>
@@ -2990,48 +3175,48 @@
       <c r="C31" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="15" t="s">
         <v>67</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="F31" s="16" t="s">
+      <c r="F31" s="15" t="s">
         <v>58</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="H31" s="16"/>
+      <c r="H31" s="15"/>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D33" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E33" s="15" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="E34" s="15" t="s">
         <v>127</v>
       </c>
     </row>
@@ -3050,64 +3235,64 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N48"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="16.25" style="15" customWidth="1"/>
-    <col min="6" max="6" width="32.875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" style="14" customWidth="1"/>
+    <col min="6" max="6" width="32.88671875" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="15" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="16" t="s">
+      <c r="D4" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="15" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="16" t="s">
+      <c r="D5" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="15" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="15" t="s">
         <v>119</v>
       </c>
     </row>
@@ -3129,19 +3314,19 @@
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="16" t="s">
+      <c r="D11" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="15" t="s">
         <v>133</v>
       </c>
     </row>
@@ -3163,19 +3348,19 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="D13" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="16" t="s">
+      <c r="D13" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="15" t="s">
         <v>133</v>
       </c>
     </row>
@@ -3279,19 +3464,19 @@
       </c>
     </row>
     <row r="20" spans="2:6">
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="15" t="s">
         <v>82</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="16" t="s">
+      <c r="D20" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="15" t="s">
         <v>148</v>
       </c>
     </row>
@@ -3420,101 +3605,101 @@
       <c r="F28" s="33"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="15" t="s">
         <v>117</v>
       </c>
       <c r="F29" s="33"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D30" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="15" t="s">
         <v>175</v>
       </c>
       <c r="F30" s="33"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="15" t="s">
         <v>176</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="15" t="s">
         <v>117</v>
       </c>
       <c r="F31" s="33"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="F32" s="14"/>
+      <c r="F32" s="13"/>
     </row>
     <row r="33" spans="2:14">
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D33" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E33" s="10" t="s">
+      <c r="D33" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="F33" s="16" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="34" spans="2:14">
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="D34" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E34" s="10" t="s">
+      <c r="D34" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="F34" s="16" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="36" spans="2:14" ht="36" customHeight="1">
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="15" t="s">
         <v>182</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="D36" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E36" s="16" t="s">
+      <c r="D36" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E36" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="F36" s="16" t="s">
+      <c r="F36" s="15" t="s">
         <v>184</v>
       </c>
       <c r="G36" s="32" t="s">
@@ -3529,13 +3714,13 @@
       <c r="N36" s="34"/>
     </row>
     <row r="37" spans="2:14">
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="15" t="s">
         <v>186</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D37" s="15" t="s">
         <v>174</v>
       </c>
       <c r="E37" s="7" t="s">
@@ -3553,7 +3738,7 @@
       <c r="N37" s="34"/>
     </row>
     <row r="39" spans="2:14">
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="15" t="s">
         <v>190</v>
       </c>
     </row>
@@ -3701,539 +3886,539 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F63"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="18.5" style="15" customWidth="1"/>
-    <col min="6" max="6" width="21.875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" style="14" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="15" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="16" t="s">
+      <c r="D4" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="15" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="16" t="s">
+      <c r="D5" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="15" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="15" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="C10" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="16">
+      <c r="C10" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="15">
         <v>10</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="15">
         <v>0</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="15" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="C11" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="16">
+      <c r="C11" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="15">
         <v>10</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <v>0</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="15" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="15">
         <v>6</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="15">
         <v>0</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="15" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="C13" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="16">
+      <c r="C13" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="15">
         <v>4</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="15">
         <v>0</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="15" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="C14" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="16">
+      <c r="C14" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="15">
         <v>4</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="15">
         <v>0</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="15" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="C15" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="16">
+      <c r="C15" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="15">
         <v>1</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="15">
         <v>0</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="15" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="C16" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="16">
+      <c r="C16" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="15">
         <v>10</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="15">
         <v>0</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="15" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="15">
         <v>5</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="15">
         <v>0</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="15" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C18" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="16">
+      <c r="C18" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="15">
         <v>4</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="15">
         <v>0</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="15" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="19" spans="2:6">
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="16">
+      <c r="C19" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="15">
         <v>18</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="15">
         <v>0</v>
       </c>
-      <c r="F19" s="16" t="s">
+      <c r="F19" s="15" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="20" spans="2:6">
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="C20" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="16">
+      <c r="C20" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="15">
         <v>18</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="15">
         <v>0</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="15" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="21" spans="2:6">
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="16">
+      <c r="C21" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="15">
         <v>10</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="15">
         <v>0</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="F21" s="15" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="22" spans="2:6">
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="C22" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="16">
+      <c r="C22" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="15">
         <v>20</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="15">
         <v>0</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="15" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="23" spans="2:6">
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="C23" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" s="16">
+      <c r="C23" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="15">
         <v>4</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="15">
         <v>0</v>
       </c>
-      <c r="F23" s="16" t="s">
+      <c r="F23" s="15" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="24" spans="2:6">
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="C24" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="16">
+      <c r="C24" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="15">
         <v>4</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="15">
         <v>0</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="15" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="25" spans="2:6">
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="C25" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="16">
+      <c r="C25" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="15">
         <v>1</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="15">
         <v>0</v>
       </c>
-      <c r="F25" s="16" t="s">
+      <c r="F25" s="15" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="26" spans="2:6">
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C26" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" s="16">
+      <c r="C26" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="15">
         <v>3</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="15">
         <v>0</v>
       </c>
-      <c r="F26" s="16" t="s">
+      <c r="F26" s="15" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="15">
         <v>13</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="15">
         <v>3</v>
       </c>
-      <c r="F27" s="16" t="s">
+      <c r="F27" s="15" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="28" spans="2:6">
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="15">
         <v>3</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="15">
         <v>0</v>
       </c>
-      <c r="F28" s="16" t="s">
+      <c r="F28" s="15" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="29" spans="2:6">
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="15">
         <v>13</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="15">
         <v>3</v>
       </c>
-      <c r="F29" s="16" t="s">
+      <c r="F29" s="15" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="15">
         <v>13</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="15">
         <v>3</v>
       </c>
-      <c r="F30" s="16" t="s">
+      <c r="F30" s="15" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="31" spans="2:6">
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="C31" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D31" s="16">
+      <c r="C31" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="15">
         <v>10</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="15">
         <v>0</v>
       </c>
-      <c r="F31" s="16" t="s">
+      <c r="F31" s="15" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="32" spans="2:6">
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="15">
         <v>13</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="15">
         <v>3</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="F32" s="15" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="33" spans="2:6">
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="15">
         <v>13</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="15">
         <v>3</v>
       </c>
-      <c r="F33" s="16" t="s">
+      <c r="F33" s="15" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="34" spans="2:6">
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="15">
         <v>13</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="15">
         <v>3</v>
       </c>
-      <c r="F34" s="16" t="s">
+      <c r="F34" s="15" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="35" spans="2:6">
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="15">
         <v>13</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="15">
         <v>3</v>
       </c>
-      <c r="F35" s="16" t="s">
+      <c r="F35" s="15" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="15">
         <v>8</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="15">
         <v>0</v>
       </c>
-      <c r="F36" s="16" t="s">
+      <c r="F36" s="15" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="37" spans="2:6">
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="D37" s="16">
+      <c r="D37" s="15">
         <v>4</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E37" s="15">
         <v>0</v>
       </c>
-      <c r="F37" s="16" t="s">
+      <c r="F37" s="15" t="s">
         <v>242</v>
       </c>
     </row>
@@ -4255,427 +4440,427 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D39" s="16">
+      <c r="D39" s="15">
         <v>8</v>
       </c>
-      <c r="E39" s="16">
+      <c r="E39" s="15">
         <v>0</v>
       </c>
-      <c r="F39" s="16" t="s">
+      <c r="F39" s="15" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="15">
         <v>8</v>
       </c>
-      <c r="E40" s="16">
+      <c r="E40" s="15">
         <v>0</v>
       </c>
-      <c r="F40" s="16" t="s">
+      <c r="F40" s="15" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C41" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D41" s="16">
+      <c r="C41" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" s="15">
         <v>30</v>
       </c>
-      <c r="E41" s="16">
+      <c r="E41" s="15">
         <v>0</v>
       </c>
-      <c r="F41" s="16" t="s">
+      <c r="F41" s="15" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="42" spans="2:6">
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C42" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D42" s="16">
+      <c r="C42" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" s="15">
         <v>30</v>
       </c>
-      <c r="E42" s="16">
+      <c r="E42" s="15">
         <v>0</v>
       </c>
-      <c r="F42" s="16" t="s">
+      <c r="F42" s="15" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="C43" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D43" s="16">
+      <c r="C43" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="15">
         <v>25</v>
       </c>
-      <c r="E43" s="16">
+      <c r="E43" s="15">
         <v>0</v>
       </c>
-      <c r="F43" s="16" t="s">
+      <c r="F43" s="15" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="C44" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D44" s="16">
+      <c r="C44" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" s="15">
         <v>40</v>
       </c>
-      <c r="E44" s="16">
+      <c r="E44" s="15">
         <v>0</v>
       </c>
-      <c r="F44" s="16" t="s">
+      <c r="F44" s="15" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="45" spans="2:6">
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="C45" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D45" s="16">
+      <c r="C45" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D45" s="15">
         <v>50</v>
       </c>
-      <c r="E45" s="16">
+      <c r="E45" s="15">
         <v>0</v>
       </c>
-      <c r="F45" s="16" t="s">
+      <c r="F45" s="15" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="46" spans="2:6">
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="C46" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D46" s="16">
+      <c r="C46" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D46" s="15">
         <v>50</v>
       </c>
-      <c r="E46" s="16">
+      <c r="E46" s="15">
         <v>0</v>
       </c>
-      <c r="F46" s="16" t="s">
+      <c r="F46" s="15" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C47" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D47" s="16">
+      <c r="C47" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D47" s="15">
         <v>16</v>
       </c>
-      <c r="E47" s="16">
+      <c r="E47" s="15">
         <v>0</v>
       </c>
-      <c r="F47" s="16" t="s">
+      <c r="F47" s="15" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="48" spans="2:6">
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="C48" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D48" s="16">
+      <c r="C48" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48" s="15">
         <v>60</v>
       </c>
-      <c r="E48" s="16">
+      <c r="E48" s="15">
         <v>0</v>
       </c>
-      <c r="F48" s="16" t="s">
+      <c r="F48" s="15" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="49" spans="2:6">
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="C49" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D49" s="16">
+      <c r="C49" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D49" s="15">
         <v>20</v>
       </c>
-      <c r="E49" s="16">
+      <c r="E49" s="15">
         <v>0</v>
       </c>
-      <c r="F49" s="16" t="s">
+      <c r="F49" s="15" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="C50" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" s="16">
+      <c r="C50" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" s="15">
         <v>20</v>
       </c>
-      <c r="E50" s="16">
+      <c r="E50" s="15">
         <v>0</v>
       </c>
-      <c r="F50" s="16" t="s">
+      <c r="F50" s="15" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="C51" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D51" s="16">
+      <c r="C51" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51" s="15">
         <v>20</v>
       </c>
-      <c r="E51" s="16">
+      <c r="E51" s="15">
         <v>0</v>
       </c>
-      <c r="F51" s="16" t="s">
+      <c r="F51" s="15" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C52" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D52" s="16">
+      <c r="D52" s="15">
         <v>13</v>
       </c>
-      <c r="E52" s="16">
+      <c r="E52" s="15">
         <v>3</v>
       </c>
-      <c r="F52" s="16" t="s">
+      <c r="F52" s="15" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="53" spans="2:6">
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="15">
         <v>3</v>
       </c>
-      <c r="E53" s="16">
+      <c r="E53" s="15">
         <v>0</v>
       </c>
-      <c r="F53" s="16" t="s">
+      <c r="F53" s="15" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="15" t="s">
         <v>272</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="D54" s="16">
+      <c r="D54" s="15">
         <v>0</v>
       </c>
-      <c r="E54" s="16">
+      <c r="E54" s="15">
         <v>0</v>
       </c>
-      <c r="F54" s="16" t="s">
+      <c r="F54" s="15" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="C55" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D55" s="16">
+      <c r="C55" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D55" s="15">
         <v>12</v>
       </c>
-      <c r="E55" s="16">
+      <c r="E55" s="15">
         <v>0</v>
       </c>
-      <c r="F55" s="16" t="s">
+      <c r="F55" s="15" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="56" spans="2:6">
-      <c r="B56" s="16" t="s">
+      <c r="B56" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="C56" s="16" t="s">
+      <c r="C56" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D56" s="16">
+      <c r="D56" s="15">
         <v>8</v>
       </c>
-      <c r="E56" s="16">
+      <c r="E56" s="15">
         <v>0</v>
       </c>
-      <c r="F56" s="16" t="s">
+      <c r="F56" s="15" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="16" t="s">
+      <c r="B57" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="C57" s="16" t="s">
+      <c r="C57" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="D57" s="16">
+      <c r="D57" s="15">
         <v>6</v>
       </c>
-      <c r="E57" s="16">
+      <c r="E57" s="15">
         <v>0</v>
       </c>
-      <c r="F57" s="16" t="s">
+      <c r="F57" s="15" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="16" t="s">
+      <c r="B58" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D58" s="16">
+      <c r="C58" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" s="15">
         <v>12</v>
       </c>
-      <c r="E58" s="16">
+      <c r="E58" s="15">
         <v>0</v>
       </c>
-      <c r="F58" s="16" t="s">
+      <c r="F58" s="15" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="59" spans="2:6">
-      <c r="B59" s="16" t="s">
+      <c r="B59" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="C59" s="16" t="s">
+      <c r="C59" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D59" s="16">
+      <c r="D59" s="15">
         <v>8</v>
       </c>
-      <c r="E59" s="16">
+      <c r="E59" s="15">
         <v>0</v>
       </c>
-      <c r="F59" s="16" t="s">
+      <c r="F59" s="15" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="60" spans="2:6">
-      <c r="B60" s="16" t="s">
+      <c r="B60" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="C60" s="16" t="s">
+      <c r="C60" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="D60" s="16">
+      <c r="D60" s="15">
         <v>6</v>
       </c>
-      <c r="E60" s="16">
+      <c r="E60" s="15">
         <v>0</v>
       </c>
-      <c r="F60" s="16" t="s">
+      <c r="F60" s="15" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="16" t="s">
+      <c r="B61" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="C61" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D61" s="16">
+      <c r="C61" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D61" s="15">
         <v>1</v>
       </c>
-      <c r="E61" s="16">
+      <c r="E61" s="15">
         <v>0</v>
       </c>
-      <c r="F61" s="16" t="s">
+      <c r="F61" s="15" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="62" spans="2:6">
-      <c r="B62" s="16" t="s">
+      <c r="B62" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="C62" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D62" s="16">
+      <c r="C62" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="15">
         <v>1</v>
       </c>
-      <c r="E62" s="16">
+      <c r="E62" s="15">
         <v>0</v>
       </c>
-      <c r="F62" s="16" t="s">
+      <c r="F62" s="15" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="63" spans="2:6">
-      <c r="B63" s="16" t="s">
+      <c r="B63" s="15" t="s">
         <v>187</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="D63" s="16">
+      <c r="D63" s="15">
         <v>13</v>
       </c>
-      <c r="E63" s="16">
+      <c r="E63" s="15">
         <v>9</v>
       </c>
-      <c r="F63" s="16" t="s">
+      <c r="F63" s="15" t="s">
         <v>186</v>
       </c>
     </row>
@@ -4686,363 +4871,799 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="16" t="s">
-        <v>301</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:O24"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Q32"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="14" style="15" customWidth="1"/>
+    <col min="2" max="2" width="14" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:17">
+      <c r="A1" s="48" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="16" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="41" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="B4" s="16" t="s">
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="41"/>
+      <c r="B4" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="16" t="s">
+      <c r="D4" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="41" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="B5" s="16" t="s">
+      <c r="F4" s="50" t="s">
+        <v>348</v>
+      </c>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" s="41"/>
+      <c r="B5" s="49" t="s">
         <v>291</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="16" t="s">
+      <c r="C5" s="41" t="s">
+        <v>330</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="41" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="B6" s="16" t="s">
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="41"/>
+      <c r="B6" s="49" t="s">
         <v>293</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="41" t="s">
+        <v>331</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="41" t="s">
         <v>294</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="41"/>
+      <c r="B7" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="41"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="41"/>
+      <c r="B8" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E8" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="41"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="41"/>
+      <c r="Q8" s="41"/>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="41"/>
+      <c r="B9" s="41" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="41" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="B7" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="16" t="s">
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="41"/>
+      <c r="Q9" s="41"/>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="41"/>
+      <c r="B10" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="41" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="B8" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="16" t="s">
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="41"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="41"/>
+      <c r="B11" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="41"/>
+      <c r="N11" s="41"/>
+      <c r="O11" s="41"/>
+      <c r="P11" s="41"/>
+      <c r="Q11" s="41"/>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="41"/>
+      <c r="B12" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="41"/>
+      <c r="M12" s="41"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="41"/>
+      <c r="P12" s="41"/>
+      <c r="Q12" s="41"/>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="41"/>
+      <c r="B13" s="41" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="41"/>
+      <c r="P13" s="41"/>
+      <c r="Q13" s="41"/>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="41"/>
+      <c r="B14" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="41"/>
+      <c r="N14" s="41"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="41"/>
+      <c r="Q14" s="41"/>
+    </row>
+    <row r="15" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A15" s="41"/>
+      <c r="B15" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="K15" s="51"/>
+      <c r="L15" s="51"/>
+      <c r="M15" s="51"/>
+      <c r="N15" s="51"/>
+      <c r="O15" s="51"/>
+      <c r="P15" s="41"/>
+      <c r="Q15" s="41"/>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="41"/>
+      <c r="B16" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="51"/>
+      <c r="L16" s="51"/>
+      <c r="M16" s="51"/>
+      <c r="N16" s="51"/>
+      <c r="O16" s="51"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="41"/>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="41"/>
+      <c r="B17" s="41" t="s">
+        <v>297</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>298</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" s="41" t="s">
+        <v>188</v>
+      </c>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
+      <c r="L17" s="51"/>
+      <c r="M17" s="51"/>
+      <c r="N17" s="51"/>
+      <c r="O17" s="51"/>
+      <c r="P17" s="41"/>
+      <c r="Q17" s="41"/>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18" s="41"/>
+      <c r="B18" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="51"/>
+      <c r="M18" s="51"/>
+      <c r="N18" s="51"/>
+      <c r="O18" s="51"/>
+      <c r="P18" s="41"/>
+      <c r="Q18" s="41"/>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" s="41"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+      <c r="L19" s="51"/>
+      <c r="M19" s="51"/>
+      <c r="N19" s="51"/>
+      <c r="O19" s="51"/>
+      <c r="P19" s="41"/>
+      <c r="Q19" s="41"/>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="41"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
+      <c r="L20" s="51"/>
+      <c r="M20" s="51"/>
+      <c r="N20" s="51"/>
+      <c r="O20" s="51"/>
+      <c r="P20" s="41"/>
+      <c r="Q20" s="41"/>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" s="41"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="51"/>
+      <c r="N21" s="51"/>
+      <c r="O21" s="51"/>
+      <c r="P21" s="41"/>
+      <c r="Q21" s="41"/>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="51"/>
+      <c r="L22" s="51"/>
+      <c r="M22" s="51"/>
+      <c r="N22" s="51"/>
+      <c r="O22" s="51"/>
+      <c r="P22" s="41"/>
+      <c r="Q22" s="41"/>
+    </row>
+    <row r="23" spans="1:17" ht="34.950000000000003" customHeight="1">
+      <c r="A23" s="41"/>
+      <c r="B23" s="52" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>125</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="E23" s="54" t="s">
+        <v>349</v>
+      </c>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="51"/>
+      <c r="M23" s="51"/>
+      <c r="N23" s="51"/>
+      <c r="O23" s="51"/>
+      <c r="P23" s="41"/>
+      <c r="Q23" s="41"/>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" s="41"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="55" t="s">
+        <v>127</v>
+      </c>
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="51"/>
+      <c r="L24" s="51"/>
+      <c r="M24" s="51"/>
+      <c r="N24" s="51"/>
+      <c r="O24" s="51"/>
+      <c r="P24" s="41"/>
+      <c r="Q24" s="41"/>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="41"/>
+      <c r="B25" s="56" t="s">
+        <v>291</v>
+      </c>
+      <c r="C25" s="56" t="s">
+        <v>330</v>
+      </c>
+      <c r="D25" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="56" t="s">
+        <v>166</v>
+      </c>
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="41"/>
+      <c r="L25" s="41"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="41"/>
+      <c r="P25" s="41"/>
+      <c r="Q25" s="41"/>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" s="41"/>
+      <c r="B26" s="56" t="s">
+        <v>293</v>
+      </c>
+      <c r="C26" s="56" t="s">
+        <v>331</v>
+      </c>
+      <c r="D26" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E26" s="56" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="56"/>
+      <c r="G26" s="56"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="57" t="s">
+        <v>350</v>
+      </c>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="41"/>
+      <c r="P26" s="41"/>
+      <c r="Q26" s="41"/>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" s="41"/>
+      <c r="B27" s="56" t="s">
+        <v>351</v>
+      </c>
+      <c r="C27" s="56" t="s">
+        <v>302</v>
+      </c>
+      <c r="D27" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="57"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" s="41"/>
+      <c r="B28" s="56" t="s">
+        <v>352</v>
+      </c>
+      <c r="C28" s="56" t="s">
+        <v>305</v>
+      </c>
+      <c r="D28" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="56" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="B9" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="B10" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="B11" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="B12" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="B13" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="B14" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="B15" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="J15" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="B16" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="34"/>
-    </row>
-    <row r="17" spans="1:15">
-      <c r="B17" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="34"/>
-    </row>
-    <row r="18" spans="1:15">
-      <c r="B18" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="34"/>
-    </row>
-    <row r="19" spans="1:15">
-      <c r="J19" s="34"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="34"/>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-    </row>
-    <row r="21" spans="1:15">
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="34"/>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="34"/>
-      <c r="O22" s="34"/>
-    </row>
-    <row r="23" spans="1:15" ht="34.9" customHeight="1">
-      <c r="B23" s="38" t="s">
-        <v>124</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="E23" s="40" t="s">
-        <v>300</v>
-      </c>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
-      <c r="O23" s="34"/>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="B24" s="33"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="J24" s="34"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="34"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="34"/>
-      <c r="O24" s="34"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="57"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29" s="41"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="A30" s="41"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="41"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31" s="41"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
+      <c r="K31" s="41"/>
+      <c r="L31" s="41"/>
+      <c r="M31" s="41"/>
+      <c r="N31" s="41"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+    </row>
+    <row r="32" spans="1:17">
+      <c r="A32" s="41"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="41"/>
+      <c r="L32" s="41"/>
+      <c r="M32" s="41"/>
+      <c r="N32" s="41"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="J26:M28"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="E23:G23"/>
@@ -5055,172 +5676,577 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:O23"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="8.77734375" style="41"/>
+    <col min="2" max="2" width="14" style="41" customWidth="1"/>
+    <col min="3" max="16384" width="8.77734375" style="41"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="41" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="41" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="B4" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="41" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="B5" s="42" t="s">
+        <v>291</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>330</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="B6" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>331</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="B7" s="43" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>333</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="B8" s="42"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="41" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="B11" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="46"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="B12" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="46"/>
+      <c r="O12" s="46"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="B13" s="42" t="s">
+        <v>291</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>330</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="41" t="s">
+        <v>166</v>
+      </c>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="46"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="46"/>
+      <c r="N13" s="46"/>
+      <c r="O13" s="46"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="B14" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>331</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="46"/>
+      <c r="O14" s="46"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="B15" s="41" t="s">
+        <v>335</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="G15" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="37"/>
+      <c r="M15" s="37"/>
+      <c r="N15" s="37"/>
+      <c r="O15" s="37"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="B16" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="37"/>
+      <c r="M16" s="37"/>
+      <c r="N16" s="37"/>
+      <c r="O16" s="37"/>
+    </row>
+    <row r="17" spans="2:15">
+      <c r="B17" s="41" t="s">
+        <v>301</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>302</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="37"/>
+      <c r="N17" s="37"/>
+      <c r="O17" s="37"/>
+    </row>
+    <row r="18" spans="2:15">
+      <c r="B18" s="41" t="s">
+        <v>337</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>305</v>
+      </c>
+      <c r="D18" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="37"/>
+      <c r="M18" s="37"/>
+      <c r="N18" s="37"/>
+      <c r="O18" s="37"/>
+    </row>
+    <row r="19" spans="2:15">
+      <c r="B19" s="41" t="s">
+        <v>338</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>339</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
+      <c r="M19" s="37"/>
+      <c r="N19" s="37"/>
+      <c r="O19" s="37"/>
+    </row>
+    <row r="20" spans="2:15">
+      <c r="B20" s="41" t="s">
+        <v>340</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>341</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="37"/>
+      <c r="M20" s="37"/>
+      <c r="N20" s="37"/>
+      <c r="O20" s="37"/>
+    </row>
+    <row r="21" spans="2:15">
+      <c r="B21" s="41" t="s">
+        <v>342</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="D21" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="37"/>
+      <c r="N21" s="37"/>
+      <c r="O21" s="37"/>
+    </row>
+    <row r="22" spans="2:15">
+      <c r="B22" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>345</v>
+      </c>
+      <c r="D22" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="37"/>
+      <c r="M22" s="37"/>
+      <c r="N22" s="37"/>
+      <c r="O22" s="37"/>
+    </row>
+    <row r="23" spans="2:15">
+      <c r="B23" s="41" t="s">
+        <v>346</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>347</v>
+      </c>
+      <c r="D23" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
+      <c r="M23" s="37"/>
+      <c r="N23" s="37"/>
+      <c r="O23" s="37"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G15:O23"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="16" customWidth="1"/>
-    <col min="2" max="2" width="14" style="16" customWidth="1"/>
-    <col min="3" max="3" width="8.75" style="16" customWidth="1"/>
-    <col min="4" max="16384" width="8.75" style="16"/>
+    <col min="1" max="1" width="8.77734375" style="15" customWidth="1"/>
+    <col min="2" max="2" width="14" style="15" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375" style="15" customWidth="1"/>
+    <col min="4" max="16384" width="8.77734375" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:11" s="41" customFormat="1">
+      <c r="A1" s="41" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="41" customFormat="1">
+      <c r="B2" s="41" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="41" customFormat="1"/>
+    <row r="4" spans="1:11" s="41" customFormat="1">
+      <c r="A4" s="41" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="41" customFormat="1">
+      <c r="B5" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="50" t="s">
+        <v>348</v>
+      </c>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+    </row>
+    <row r="6" spans="1:11" s="41" customFormat="1">
+      <c r="B6" s="49" t="s">
+        <v>301</v>
+      </c>
+      <c r="C6" s="41" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="B4" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="B5" s="16" t="s">
+      <c r="D6" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="G6" s="37" t="s">
         <v>303</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+    </row>
+    <row r="7" spans="1:11" s="41" customFormat="1">
+      <c r="B7" s="49" t="s">
         <v>304</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="16" t="s">
+      <c r="C7" s="41" t="s">
+        <v>305</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+    </row>
+    <row r="8" spans="1:11" s="41" customFormat="1">
+      <c r="B8" s="41" t="s">
+        <v>306</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>194</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="G5" s="37" t="s">
-        <v>305</v>
-      </c>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="B6" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="C6" s="16" t="s">
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
+    </row>
+    <row r="9" spans="1:11" s="41" customFormat="1">
+      <c r="B9" s="41" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+    </row>
+    <row r="10" spans="1:11" s="41" customFormat="1">
+      <c r="B10" s="41" t="s">
         <v>307</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="C10" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="D10" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="B7" s="16" t="s">
-        <v>308</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="34"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="B8" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="B9" s="16" t="s">
-        <v>309</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="16" t="s">
+      <c r="E10" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="16" t="s">
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+    </row>
+    <row r="11" spans="1:11" s="41" customFormat="1"/>
+    <row r="12" spans="1:11" s="41" customFormat="1">
+      <c r="A12" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="D11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="16">
+      <c r="D12" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="41">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
-      <c r="B12" s="16" t="s">
+    <row r="13" spans="1:11" s="41" customFormat="1">
+      <c r="B13" s="58" t="s">
         <v>124</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C13" s="58" t="s">
         <v>125</v>
       </c>
-      <c r="D12" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="16">
+      <c r="D13" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="41">
         <v>220</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="G5:K9"/>
+  <mergeCells count="2">
+    <mergeCell ref="G5:K5"/>
+    <mergeCell ref="G6:K10"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5229,66 +6255,162 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="16" customWidth="1"/>
-    <col min="2" max="16384" width="8.75" style="16"/>
+    <col min="1" max="1" width="8.77734375" style="15" customWidth="1"/>
+    <col min="2" max="16384" width="8.77734375" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="41" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="16" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="16" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="41" t="s">
+        <v>308</v>
+      </c>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="41"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="16" t="s">
+      <c r="B5" s="59" t="s">
+        <v>353</v>
+      </c>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="41"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="D7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="16">
+      <c r="D7" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="41">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="B8" s="16" t="s">
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="41"/>
+      <c r="B8" s="58" t="s">
         <v>124</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="58" t="s">
         <v>125</v>
       </c>
-      <c r="D8" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="16">
+      <c r="D8" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="41">
         <v>220</v>
       </c>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="41"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B5" location="'A-LM-ABAP-WMZC592'!A1" display="同链接输出内容" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
+    <hyperlink ref="B5" location="'A-LM-ABAP-WMZC592'!A1" display="同链接输出内容" xr:uid="{1F6F9ABE-5A09-4B6D-ACDB-3174D1BB5D64}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/aspnet-core/prototype/领用配送接口FS(2).xlsx
+++ b/aspnet-core/prototype/领用配送接口FS(2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\module-zero-core-template\aspnet-core\prototype\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB205291-D54E-4041-9780-6D51ECB5815E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7CDA271-C138-473E-84D6-945F7EC2FA34}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6948" tabRatio="669" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6948" tabRatio="669" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="目录" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="359">
   <si>
     <t>A-LM-ABAP-WMZC588</t>
   </si>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>库存接口，WCT调SAP，</t>
-  </si>
-  <si>
-    <t>LM-INT-WCT-063</t>
   </si>
   <si>
     <t>A-LM-ABAP-WMZC592</t>
@@ -1231,6 +1228,26 @@
   </si>
   <si>
     <t>LM-INT-WCT-071</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LM-INT-WCT-063</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZCCBZ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>存储包装方式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHAR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>25,0</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1503,7 +1520,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1599,24 +1616,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1633,18 +1632,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1655,18 +1677,20 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2076,62 +2100,62 @@
       <c r="B5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="15" t="s">
-        <v>10</v>
+      <c r="D5" s="7" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="D6" s="7" t="s">
         <v>12</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="D7" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>18</v>
-      </c>
       <c r="D8" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>20</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>21</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="15"/>
       <c r="B10" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
@@ -2139,31 +2163,31 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
         <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="15" t="s">
         <v>26</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2179,330 +2203,330 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="B4" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>130</v>
-      </c>
       <c r="D4" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="B5" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>292</v>
-      </c>
       <c r="D5" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="B6" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>63</v>
-      </c>
       <c r="D6" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="B7" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="D7" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="E7" s="15" t="s">
         <v>67</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="B8" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>70</v>
-      </c>
       <c r="D8" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="15" customFormat="1">
       <c r="B9" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>81</v>
-      </c>
       <c r="D9" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="G9" s="40" t="s">
-        <v>310</v>
+        <v>135</v>
+      </c>
+      <c r="G9" s="60" t="s">
+        <v>309</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="15" customFormat="1">
       <c r="B10" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>83</v>
-      </c>
       <c r="D10" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="G10" s="34"/>
+        <v>146</v>
+      </c>
+      <c r="G10" s="49"/>
       <c r="H10" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="B11" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>312</v>
-      </c>
       <c r="D11" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="33"/>
+      <c r="G11" s="48"/>
       <c r="H11" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="B12" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="D12" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="E12" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="E12" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="G12" s="33"/>
+      <c r="G12" s="48"/>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8" s="15" customFormat="1">
       <c r="B13" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13" s="34"/>
+        <v>63</v>
+      </c>
+      <c r="G13" s="49"/>
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" s="2" customFormat="1">
       <c r="B14" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:8">
       <c r="B15" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="D15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>165</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="B16" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>168</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="B17" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>86</v>
-      </c>
       <c r="D17" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="B18" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D18" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E18" s="15" t="s">
         <v>92</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="B19" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="D19" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="15" t="s">
         <v>103</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="B20" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D20" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" s="15" t="s">
         <v>92</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1">
       <c r="B21" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1">
       <c r="B22" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1">
       <c r="B23" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1">
       <c r="B24" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="D24" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="G24" s="6"/>
     </row>
@@ -2512,43 +2536,43 @@
     <row r="26" spans="1:7" s="15" customFormat="1"/>
     <row r="27" spans="1:7">
       <c r="A27" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="C27" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="D27" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="E27" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="E27" s="15" t="s">
+    </row>
+    <row r="28" spans="1:7">
+      <c r="B28" s="62" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="B28" s="38" t="s">
+      <c r="C28" s="61" t="s">
         <v>124</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="D28" s="61" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="39" t="s">
+      <c r="E28" s="60" t="s">
+        <v>317</v>
+      </c>
+      <c r="F28" s="49"/>
+      <c r="G28" s="48"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="B29" s="48"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="15" t="s">
         <v>126</v>
-      </c>
-      <c r="E28" s="40" t="s">
-        <v>318</v>
-      </c>
-      <c r="F28" s="34"/>
-      <c r="G28" s="33"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="B29" s="33"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="15" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -2580,175 +2604,175 @@
   <sheetData>
     <row r="1" spans="2:6" ht="30" customHeight="1">
       <c r="B1" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="16.2" customHeight="1">
       <c r="B2" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="24" customHeight="1">
       <c r="B3" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>33</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="66" customHeight="1">
       <c r="B5" s="22" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="16.2" customHeight="1">
       <c r="D6" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="66" customHeight="1">
       <c r="D7" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="16.2" customHeight="1">
       <c r="D8" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="66" customHeight="1">
       <c r="C9" s="23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="16.2" customHeight="1">
       <c r="D10" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="66" customHeight="1">
       <c r="C11" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="16.2" customHeight="1">
       <c r="D12" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="66" customHeight="1">
       <c r="D13" s="25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="16.2" customHeight="1">
       <c r="D14" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="66" customHeight="1">
       <c r="D15" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="16.2" customHeight="1">
       <c r="D16" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="66" customHeight="1">
       <c r="C17" s="23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="16.2" customHeight="1">
       <c r="D18" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="66" customHeight="1">
       <c r="C19" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="16.2" customHeight="1">
       <c r="D20" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="66" customHeight="1">
       <c r="D21" s="26" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="16.2" customHeight="1">
       <c r="D22" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="66" customHeight="1">
       <c r="E23" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" s="28" t="s">
         <v>45</v>
-      </c>
-      <c r="F23" s="28" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="16.2" customHeight="1">
       <c r="D24" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="66" customHeight="1">
       <c r="B25" s="31" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="2:6" ht="16.2" customHeight="1">
       <c r="D26" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="2:6" ht="66" customHeight="1">
       <c r="D27" s="25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="2:6" ht="16.2" customHeight="1">
       <c r="D28" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="2:6" ht="66" customHeight="1">
       <c r="C29" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2773,451 +2797,451 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
+      <c r="A3" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="48"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="9" customFormat="1">
       <c r="B10" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>55</v>
-      </c>
       <c r="D10" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="F10" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="5" customFormat="1">
       <c r="B11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="9" customFormat="1">
       <c r="B12" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="D12" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>64</v>
-      </c>
       <c r="F12" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="B13" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="D13" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="E13" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="15" t="s">
-        <v>68</v>
-      </c>
       <c r="F13" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="B14" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="D14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D14" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>71</v>
-      </c>
       <c r="F14" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="B15" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="D15" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="E15" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="15" t="s">
-        <v>75</v>
-      </c>
       <c r="F15" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="B16" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="D16" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="E16" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="15" t="s">
-        <v>79</v>
-      </c>
       <c r="F16" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>81</v>
-      </c>
       <c r="D17" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="D18" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>84</v>
-      </c>
       <c r="F18" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="2:8" s="29" customFormat="1">
       <c r="B19" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19" s="30" t="s">
         <v>321</v>
-      </c>
-      <c r="D19" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19" s="30" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C20" s="15" t="s">
-        <v>86</v>
-      </c>
       <c r="D20" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="15" t="s">
-        <v>57</v>
-      </c>
       <c r="F20" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="2:8" s="15" customFormat="1">
       <c r="B21" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="D21" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="22" spans="2:8" s="9" customFormat="1">
       <c r="B22" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="D22" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="E22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E22" s="9" t="s">
-        <v>93</v>
-      </c>
       <c r="F22" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="2:8">
       <c r="B23" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="D23" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="D23" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" s="15" t="s">
+      <c r="F23" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G23" s="50" t="s">
         <v>96</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G23" s="35" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="15.6" customHeight="1">
       <c r="B24" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="D24" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="E24" s="15" t="s">
-        <v>57</v>
-      </c>
       <c r="F24" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G24" s="34"/>
+        <v>60</v>
+      </c>
+      <c r="G24" s="49"/>
     </row>
     <row r="25" spans="2:8">
       <c r="B25" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="15" t="s">
-        <v>101</v>
-      </c>
       <c r="D25" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E25" s="15" t="s">
-        <v>93</v>
-      </c>
       <c r="F25" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G25" s="34"/>
+        <v>60</v>
+      </c>
+      <c r="G25" s="49"/>
     </row>
     <row r="26" spans="2:8">
       <c r="B26" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="D26" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="D26" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>104</v>
-      </c>
       <c r="F26" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G26" s="34"/>
+        <v>60</v>
+      </c>
+      <c r="G26" s="49"/>
     </row>
     <row r="27" spans="2:8" s="9" customFormat="1">
       <c r="B27" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>106</v>
-      </c>
       <c r="D27" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="2:8" s="9" customFormat="1">
       <c r="B28" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>108</v>
-      </c>
       <c r="D28" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="2:8">
       <c r="B29" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="D29" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>111</v>
-      </c>
       <c r="F29" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="2:8" s="9" customFormat="1">
       <c r="B30" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="D30" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G30" s="9" t="s">
         <v>113</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="31" spans="2:8">
       <c r="B31" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="D31" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D31" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E31" s="7" t="s">
+      <c r="F31" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G31" s="8" t="s">
         <v>117</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>118</v>
       </c>
       <c r="H31" s="15"/>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B33" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="C33" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="D33" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="E33" s="15" t="s">
         <v>122</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="B34" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="D34" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="E34" s="15" t="s">
         <v>126</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -3234,7 +3258,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="16.21875" style="14" customWidth="1"/>
@@ -3243,638 +3267,654 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="B4" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="D4" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="15" t="s">
+      <c r="G4" s="15" t="s">
         <v>131</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="D5" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>71</v>
-      </c>
       <c r="F5" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G5" s="15" t="s">
         <v>131</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1">
       <c r="B10" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="D10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="B11" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="D11" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>71</v>
-      </c>
       <c r="F11" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1">
       <c r="B12" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="D12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="B13" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>81</v>
-      </c>
       <c r="D13" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1">
       <c r="B14" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1">
       <c r="B15" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="D15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1">
       <c r="B16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="2:6" s="2" customFormat="1">
       <c r="B17" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="2:6" s="2" customFormat="1">
       <c r="B18" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="2:6" s="2" customFormat="1">
       <c r="B19" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="D20" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="F20" s="15" t="s">
         <v>147</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="21" spans="2:6" s="2" customFormat="1">
       <c r="B21" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="22" spans="2:6" s="2" customFormat="1">
       <c r="B22" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" s="47" t="s">
         <v>153</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F22" s="32" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="23" spans="2:6" s="2" customFormat="1">
       <c r="B23" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F23" s="36"/>
+      <c r="F23" s="51"/>
     </row>
     <row r="24" spans="2:6" s="2" customFormat="1">
       <c r="B24" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F24" s="36"/>
+        <v>135</v>
+      </c>
+      <c r="F24" s="51"/>
     </row>
     <row r="25" spans="2:6" s="2" customFormat="1">
       <c r="B25" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F25" s="36"/>
+        <v>56</v>
+      </c>
+      <c r="F25" s="51"/>
     </row>
     <row r="26" spans="2:6" s="2" customFormat="1">
       <c r="B26" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="D26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F26" s="36"/>
+      <c r="F26" s="51"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="D27" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="F27" s="33"/>
+      <c r="F27" s="48"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="D28" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="F28" s="33"/>
+      <c r="F28" s="48"/>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="C29" s="15" t="s">
-        <v>171</v>
-      </c>
       <c r="D29" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="F29" s="33"/>
+        <v>116</v>
+      </c>
+      <c r="F29" s="48"/>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="D30" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="E30" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="E30" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="F30" s="33"/>
+      <c r="F30" s="48"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>177</v>
-      </c>
       <c r="D31" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="F31" s="33"/>
+        <v>116</v>
+      </c>
+      <c r="F31" s="48"/>
     </row>
     <row r="32" spans="2:6">
       <c r="F32" s="13"/>
     </row>
     <row r="33" spans="2:14">
       <c r="B33" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="2:14">
       <c r="B34" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C34" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="D34" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="D34" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>181</v>
-      </c>
       <c r="F34" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="2:14" ht="36" customHeight="1">
       <c r="B36" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="D36" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F36" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="D36" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E36" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="F36" s="15" t="s">
+      <c r="G36" s="47" t="s">
         <v>184</v>
       </c>
-      <c r="G36" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="34"/>
+      <c r="H36" s="49"/>
+      <c r="I36" s="49"/>
+      <c r="J36" s="49"/>
+      <c r="K36" s="49"/>
+      <c r="L36" s="49"/>
+      <c r="M36" s="49"/>
+      <c r="N36" s="49"/>
     </row>
     <row r="37" spans="2:14">
       <c r="B37" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="D37" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="E37" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D37" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="E37" s="7" t="s">
+      <c r="G37" s="47" t="s">
         <v>188</v>
       </c>
-      <c r="G37" s="32" t="s">
+      <c r="H37" s="49"/>
+      <c r="I37" s="49"/>
+      <c r="J37" s="49"/>
+      <c r="K37" s="49"/>
+      <c r="L37" s="49"/>
+      <c r="M37" s="49"/>
+      <c r="N37" s="49"/>
+    </row>
+    <row r="38" spans="2:14" s="34" customFormat="1">
+      <c r="B38" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="F38" s="33"/>
+      <c r="G38" s="32"/>
+    </row>
+    <row r="40" spans="2:14">
+      <c r="B40" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="H37" s="34"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="34"/>
-      <c r="L37" s="34"/>
-      <c r="M37" s="34"/>
-      <c r="N37" s="34"/>
-    </row>
-    <row r="39" spans="2:14">
-      <c r="B39" s="15" t="s">
+    </row>
+    <row r="41" spans="2:14">
+      <c r="B41" s="52" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="40" spans="2:14">
-      <c r="B40" s="37" t="s">
-        <v>191</v>
-      </c>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="34"/>
-      <c r="I40" s="34"/>
-      <c r="J40" s="34"/>
-      <c r="K40" s="34"/>
-      <c r="L40" s="34"/>
-      <c r="M40" s="34"/>
-    </row>
-    <row r="41" spans="2:14">
-      <c r="B41" s="33"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="33"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="34"/>
-      <c r="I41" s="34"/>
-      <c r="J41" s="34"/>
-      <c r="K41" s="34"/>
-      <c r="L41" s="34"/>
-      <c r="M41" s="34"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="49"/>
+      <c r="H41" s="49"/>
+      <c r="I41" s="49"/>
+      <c r="J41" s="49"/>
+      <c r="K41" s="49"/>
+      <c r="L41" s="49"/>
+      <c r="M41" s="49"/>
     </row>
     <row r="42" spans="2:14">
-      <c r="B42" s="33"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="34"/>
-      <c r="K42" s="34"/>
-      <c r="L42" s="34"/>
-      <c r="M42" s="34"/>
+      <c r="B42" s="48"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="48"/>
+      <c r="G42" s="49"/>
+      <c r="H42" s="49"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="49"/>
+      <c r="K42" s="49"/>
+      <c r="L42" s="49"/>
+      <c r="M42" s="49"/>
     </row>
     <row r="43" spans="2:14">
-      <c r="B43" s="33"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="34"/>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
-      <c r="J43" s="34"/>
-      <c r="K43" s="34"/>
-      <c r="L43" s="34"/>
-      <c r="M43" s="34"/>
+      <c r="B43" s="48"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="48"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="49"/>
+      <c r="J43" s="49"/>
+      <c r="K43" s="49"/>
+      <c r="L43" s="49"/>
+      <c r="M43" s="49"/>
     </row>
     <row r="44" spans="2:14">
-      <c r="B44" s="33"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="34"/>
-      <c r="H44" s="34"/>
-      <c r="I44" s="34"/>
-      <c r="J44" s="34"/>
-      <c r="K44" s="34"/>
-      <c r="L44" s="34"/>
-      <c r="M44" s="34"/>
+      <c r="B44" s="48"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="49"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="49"/>
+      <c r="H44" s="49"/>
+      <c r="I44" s="49"/>
+      <c r="J44" s="49"/>
+      <c r="K44" s="49"/>
+      <c r="L44" s="49"/>
+      <c r="M44" s="49"/>
     </row>
     <row r="45" spans="2:14">
-      <c r="B45" s="33"/>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="34"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="34"/>
-      <c r="H45" s="34"/>
-      <c r="I45" s="34"/>
-      <c r="J45" s="34"/>
-      <c r="K45" s="34"/>
-      <c r="L45" s="34"/>
-      <c r="M45" s="34"/>
+      <c r="B45" s="48"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="48"/>
+      <c r="G45" s="49"/>
+      <c r="H45" s="49"/>
+      <c r="I45" s="49"/>
+      <c r="J45" s="49"/>
+      <c r="K45" s="49"/>
+      <c r="L45" s="49"/>
+      <c r="M45" s="49"/>
     </row>
     <row r="46" spans="2:14">
-      <c r="B46" s="33"/>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="33"/>
-      <c r="G46" s="34"/>
-      <c r="H46" s="34"/>
-      <c r="I46" s="34"/>
-      <c r="J46" s="34"/>
-      <c r="K46" s="34"/>
-      <c r="L46" s="34"/>
-      <c r="M46" s="34"/>
+      <c r="B46" s="48"/>
+      <c r="C46" s="49"/>
+      <c r="D46" s="49"/>
+      <c r="E46" s="49"/>
+      <c r="F46" s="48"/>
+      <c r="G46" s="49"/>
+      <c r="H46" s="49"/>
+      <c r="I46" s="49"/>
+      <c r="J46" s="49"/>
+      <c r="K46" s="49"/>
+      <c r="L46" s="49"/>
+      <c r="M46" s="49"/>
     </row>
     <row r="47" spans="2:14">
-      <c r="B47" s="33"/>
-      <c r="C47" s="34"/>
-      <c r="D47" s="34"/>
-      <c r="E47" s="34"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="34"/>
-      <c r="H47" s="34"/>
-      <c r="I47" s="34"/>
-      <c r="J47" s="34"/>
-      <c r="K47" s="34"/>
-      <c r="L47" s="34"/>
-      <c r="M47" s="34"/>
+      <c r="B47" s="48"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="48"/>
+      <c r="G47" s="49"/>
+      <c r="H47" s="49"/>
+      <c r="I47" s="49"/>
+      <c r="J47" s="49"/>
+      <c r="K47" s="49"/>
+      <c r="L47" s="49"/>
+      <c r="M47" s="49"/>
     </row>
     <row r="48" spans="2:14">
-      <c r="B48" s="33"/>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="33"/>
-      <c r="G48" s="34"/>
-      <c r="H48" s="34"/>
-      <c r="I48" s="34"/>
-      <c r="J48" s="34"/>
-      <c r="K48" s="34"/>
-      <c r="L48" s="34"/>
-      <c r="M48" s="34"/>
+      <c r="B48" s="48"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="48"/>
+      <c r="G48" s="49"/>
+      <c r="H48" s="49"/>
+      <c r="I48" s="49"/>
+      <c r="J48" s="49"/>
+      <c r="K48" s="49"/>
+      <c r="L48" s="49"/>
+      <c r="M48" s="49"/>
+    </row>
+    <row r="49" spans="2:13">
+      <c r="B49" s="48"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="49"/>
+      <c r="H49" s="49"/>
+      <c r="I49" s="49"/>
+      <c r="J49" s="49"/>
+      <c r="K49" s="49"/>
+      <c r="L49" s="49"/>
+      <c r="M49" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="G37:N37"/>
     <mergeCell ref="F22:F31"/>
-    <mergeCell ref="B40:M48"/>
+    <mergeCell ref="B41:M49"/>
     <mergeCell ref="G36:N36"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -3894,64 +3934,64 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="D4" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="15" t="s">
         <v>130</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="D5" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>71</v>
-      </c>
       <c r="F5" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" s="15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="B10" s="15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D10" s="15">
         <v>10</v>
@@ -3960,15 +4000,15 @@
         <v>0</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="B11" s="15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" s="15">
         <v>10</v>
@@ -3977,15 +4017,15 @@
         <v>0</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="B12" s="15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D12" s="15">
         <v>6</v>
@@ -3994,15 +4034,15 @@
         <v>0</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="B13" s="15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13" s="15">
         <v>4</v>
@@ -4011,15 +4051,15 @@
         <v>0</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="B14" s="15" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" s="15">
         <v>4</v>
@@ -4028,15 +4068,15 @@
         <v>0</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="B15" s="15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" s="15">
         <v>1</v>
@@ -4045,15 +4085,15 @@
         <v>0</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="B16" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D16" s="15">
         <v>10</v>
@@ -4062,15 +4102,15 @@
         <v>0</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="2:6">
       <c r="B17" s="15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D17" s="15">
         <v>5</v>
@@ -4079,15 +4119,15 @@
         <v>0</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" s="15">
         <v>4</v>
@@ -4096,15 +4136,15 @@
         <v>0</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" s="15">
         <v>18</v>
@@ -4113,15 +4153,15 @@
         <v>0</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D20" s="15">
         <v>18</v>
@@ -4130,15 +4170,15 @@
         <v>0</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D21" s="15">
         <v>10</v>
@@ -4147,15 +4187,15 @@
         <v>0</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="15" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" s="15">
         <v>20</v>
@@ -4164,15 +4204,15 @@
         <v>0</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D23" s="15">
         <v>4</v>
@@ -4181,15 +4221,15 @@
         <v>0</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D24" s="15">
         <v>4</v>
@@ -4198,15 +4238,15 @@
         <v>0</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D25" s="15">
         <v>1</v>
@@ -4215,15 +4255,15 @@
         <v>0</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D26" s="15">
         <v>3</v>
@@ -4232,15 +4272,15 @@
         <v>0</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D27" s="15">
         <v>13</v>
@@ -4249,15 +4289,15 @@
         <v>3</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="15" t="s">
         <v>77</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>78</v>
       </c>
       <c r="D28" s="15">
         <v>3</v>
@@ -4266,15 +4306,15 @@
         <v>0</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D29" s="15">
         <v>13</v>
@@ -4283,15 +4323,15 @@
         <v>3</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D30" s="15">
         <v>13</v>
@@ -4300,15 +4340,15 @@
         <v>3</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D31" s="15">
         <v>10</v>
@@ -4317,15 +4357,15 @@
         <v>0</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D32" s="15">
         <v>13</v>
@@ -4334,15 +4374,15 @@
         <v>3</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D33" s="15">
         <v>13</v>
@@ -4351,15 +4391,15 @@
         <v>3</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D34" s="15">
         <v>13</v>
@@ -4368,15 +4408,15 @@
         <v>3</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D35" s="15">
         <v>13</v>
@@ -4385,15 +4425,15 @@
         <v>3</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="36" spans="2:6">
       <c r="B36" s="15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D36" s="15">
         <v>8</v>
@@ -4402,15 +4442,15 @@
         <v>0</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D37" s="15">
         <v>4</v>
@@ -4419,15 +4459,15 @@
         <v>0</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="38" spans="2:6" s="2" customFormat="1">
       <c r="B38" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D38" s="2">
         <v>8</v>
@@ -4436,15 +4476,15 @@
         <v>0</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D39" s="15">
         <v>8</v>
@@ -4453,15 +4493,15 @@
         <v>0</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D40" s="15">
         <v>8</v>
@@ -4470,15 +4510,15 @@
         <v>0</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D41" s="15">
         <v>30</v>
@@ -4487,15 +4527,15 @@
         <v>0</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D42" s="15">
         <v>30</v>
@@ -4504,15 +4544,15 @@
         <v>0</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D43" s="15">
         <v>25</v>
@@ -4521,15 +4561,15 @@
         <v>0</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D44" s="15">
         <v>40</v>
@@ -4538,15 +4578,15 @@
         <v>0</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D45" s="15">
         <v>50</v>
@@ -4555,15 +4595,15 @@
         <v>0</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D46" s="15">
         <v>50</v>
@@ -4572,15 +4612,15 @@
         <v>0</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="47" spans="2:6">
       <c r="B47" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D47" s="15">
         <v>16</v>
@@ -4589,15 +4629,15 @@
         <v>0</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D48" s="15">
         <v>60</v>
@@ -4606,15 +4646,15 @@
         <v>0</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D49" s="15">
         <v>20</v>
@@ -4623,15 +4663,15 @@
         <v>0</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D50" s="15">
         <v>20</v>
@@ -4640,15 +4680,15 @@
         <v>0</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D51" s="15">
         <v>20</v>
@@ -4657,15 +4697,15 @@
         <v>0</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D52" s="15">
         <v>13</v>
@@ -4674,15 +4714,15 @@
         <v>3</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D53" s="15">
         <v>3</v>
@@ -4691,15 +4731,15 @@
         <v>0</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="C54" s="7" t="s">
         <v>272</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>273</v>
       </c>
       <c r="D54" s="15">
         <v>0</v>
@@ -4708,15 +4748,15 @@
         <v>0</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D55" s="15">
         <v>12</v>
@@ -4725,15 +4765,15 @@
         <v>0</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D56" s="15">
         <v>8</v>
@@ -4742,15 +4782,15 @@
         <v>0</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="C57" s="15" t="s">
         <v>279</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>280</v>
       </c>
       <c r="D57" s="15">
         <v>6</v>
@@ -4759,15 +4799,15 @@
         <v>0</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="15" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D58" s="15">
         <v>12</v>
@@ -4776,15 +4816,15 @@
         <v>0</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D59" s="15">
         <v>8</v>
@@ -4793,15 +4833,15 @@
         <v>0</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D60" s="15">
         <v>6</v>
@@ -4810,15 +4850,15 @@
         <v>0</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D61" s="15">
         <v>1</v>
@@ -4827,15 +4867,15 @@
         <v>0</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D62" s="15">
         <v>1</v>
@@ -4844,15 +4884,15 @@
         <v>0</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D63" s="15">
         <v>13</v>
@@ -4861,7 +4901,7 @@
         <v>9</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -4879,786 +4919,786 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="41"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
+      <c r="A3" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="41"/>
-      <c r="B4" s="49" t="s">
+      <c r="A4" s="35"/>
+      <c r="B4" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="50" t="s">
+      <c r="F4" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" s="35"/>
+      <c r="B5" s="42" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>329</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
+      <c r="P5" s="35"/>
+      <c r="Q5" s="35"/>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="35"/>
+      <c r="B6" s="42" t="s">
+        <v>292</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>330</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="35" t="s">
+        <v>293</v>
+      </c>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="35"/>
+      <c r="B7" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="35"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="35"/>
+      <c r="B8" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="35"/>
+      <c r="B9" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>294</v>
+      </c>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="35"/>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="35"/>
+      <c r="B10" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="35"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="35"/>
+      <c r="Q10" s="35"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="35"/>
+      <c r="B11" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="35"/>
+      <c r="B12" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35"/>
+      <c r="Q12" s="35"/>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="35"/>
+      <c r="B13" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="35"/>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="35"/>
+      <c r="B14" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+    </row>
+    <row r="15" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A15" s="35"/>
+      <c r="B15" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="52" t="s">
+        <v>295</v>
+      </c>
+      <c r="K15" s="58"/>
+      <c r="L15" s="58"/>
+      <c r="M15" s="58"/>
+      <c r="N15" s="58"/>
+      <c r="O15" s="58"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="35"/>
+      <c r="B16" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="58"/>
+      <c r="L16" s="58"/>
+      <c r="M16" s="58"/>
+      <c r="N16" s="58"/>
+      <c r="O16" s="58"/>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="35"/>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="35"/>
+      <c r="B17" s="35" t="s">
+        <v>296</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="58"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="58"/>
+      <c r="N17" s="58"/>
+      <c r="O17" s="58"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18" s="35"/>
+      <c r="B18" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="58"/>
+      <c r="L18" s="58"/>
+      <c r="M18" s="58"/>
+      <c r="N18" s="58"/>
+      <c r="O18" s="58"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" s="35"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="58"/>
+      <c r="K19" s="58"/>
+      <c r="L19" s="58"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="58"/>
+      <c r="O19" s="58"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="35"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
+      <c r="L20" s="58"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="58"/>
+      <c r="O20" s="58"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="35"/>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" s="35"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="58"/>
+      <c r="L21" s="58"/>
+      <c r="M21" s="58"/>
+      <c r="N21" s="58"/>
+      <c r="O21" s="58"/>
+      <c r="P21" s="35"/>
+      <c r="Q21" s="35"/>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="E22" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="58"/>
+      <c r="K22" s="58"/>
+      <c r="L22" s="58"/>
+      <c r="M22" s="58"/>
+      <c r="N22" s="58"/>
+      <c r="O22" s="58"/>
+      <c r="P22" s="35"/>
+      <c r="Q22" s="35"/>
+    </row>
+    <row r="23" spans="1:17" ht="34.950000000000003" customHeight="1">
+      <c r="A23" s="35"/>
+      <c r="B23" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" s="56" t="s">
+        <v>125</v>
+      </c>
+      <c r="E23" s="57" t="s">
         <v>348</v>
       </c>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-    </row>
-    <row r="5" spans="1:17">
-      <c r="A5" s="41"/>
-      <c r="B5" s="49" t="s">
-        <v>291</v>
-      </c>
-      <c r="C5" s="41" t="s">
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="58"/>
+      <c r="L23" s="58"/>
+      <c r="M23" s="58"/>
+      <c r="N23" s="58"/>
+      <c r="O23" s="58"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" s="35"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="58"/>
+      <c r="L24" s="58"/>
+      <c r="M24" s="58"/>
+      <c r="N24" s="58"/>
+      <c r="O24" s="58"/>
+      <c r="P24" s="35"/>
+      <c r="Q24" s="35"/>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="35"/>
+      <c r="B25" s="44" t="s">
+        <v>290</v>
+      </c>
+      <c r="C25" s="44" t="s">
+        <v>329</v>
+      </c>
+      <c r="D25" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="E25" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="35"/>
+      <c r="Q25" s="35"/>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" s="35"/>
+      <c r="B26" s="44" t="s">
+        <v>292</v>
+      </c>
+      <c r="C26" s="44" t="s">
         <v>330</v>
       </c>
-      <c r="D5" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="41" t="s">
-        <v>166</v>
-      </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41"/>
-      <c r="O5" s="41"/>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="41"/>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="A6" s="41"/>
-      <c r="B6" s="49" t="s">
-        <v>293</v>
-      </c>
-      <c r="C6" s="41" t="s">
-        <v>331</v>
-      </c>
-      <c r="D6" s="41" t="s">
+      <c r="D26" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="54" t="s">
+        <v>349</v>
+      </c>
+      <c r="K26" s="54"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="54"/>
+      <c r="N26" s="35"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="35"/>
+      <c r="Q26" s="35"/>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" s="35"/>
+      <c r="B27" s="44" t="s">
+        <v>350</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="E27" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="54"/>
+      <c r="K27" s="54"/>
+      <c r="L27" s="54"/>
+      <c r="M27" s="54"/>
+      <c r="N27" s="35"/>
+      <c r="O27" s="35"/>
+      <c r="P27" s="35"/>
+      <c r="Q27" s="35"/>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" s="35"/>
+      <c r="B28" s="44" t="s">
+        <v>351</v>
+      </c>
+      <c r="C28" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="D28" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="41" t="s">
-        <v>294</v>
-      </c>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="A7" s="41"/>
-      <c r="B7" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="41"/>
-      <c r="P7" s="41"/>
-      <c r="Q7" s="41"/>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="A8" s="41"/>
-      <c r="B8" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="41"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="41"/>
-      <c r="P8" s="41"/>
-      <c r="Q8" s="41"/>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="A9" s="41"/>
-      <c r="B9" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="41" t="s">
-        <v>295</v>
-      </c>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="41"/>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="A10" s="41"/>
-      <c r="B10" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="41"/>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="A11" s="41"/>
-      <c r="B11" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="C11" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="41" t="s">
-        <v>96</v>
-      </c>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="41"/>
-      <c r="N11" s="41"/>
-      <c r="O11" s="41"/>
-      <c r="P11" s="41"/>
-      <c r="Q11" s="41"/>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="A12" s="41"/>
-      <c r="B12" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="C12" s="41" t="s">
-        <v>180</v>
-      </c>
-      <c r="D12" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="41" t="s">
-        <v>181</v>
-      </c>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="41"/>
-      <c r="L12" s="41"/>
-      <c r="M12" s="41"/>
-      <c r="N12" s="41"/>
-      <c r="O12" s="41"/>
-      <c r="P12" s="41"/>
-      <c r="Q12" s="41"/>
-    </row>
-    <row r="13" spans="1:17">
-      <c r="A13" s="41"/>
-      <c r="B13" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="41"/>
-      <c r="O13" s="41"/>
-      <c r="P13" s="41"/>
-      <c r="Q13" s="41"/>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="A14" s="41"/>
-      <c r="B14" s="41" t="s">
-        <v>141</v>
-      </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="41"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="41"/>
-      <c r="N14" s="41"/>
-      <c r="O14" s="41"/>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="41"/>
-    </row>
-    <row r="15" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A15" s="41"/>
-      <c r="B15" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="C15" s="41" t="s">
-        <v>144</v>
-      </c>
-      <c r="D15" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="37" t="s">
-        <v>296</v>
-      </c>
-      <c r="K15" s="51"/>
-      <c r="L15" s="51"/>
-      <c r="M15" s="51"/>
-      <c r="N15" s="51"/>
-      <c r="O15" s="51"/>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="41"/>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="A16" s="41"/>
-      <c r="B16" s="41" t="s">
-        <v>145</v>
-      </c>
-      <c r="C16" s="41" t="s">
-        <v>146</v>
-      </c>
-      <c r="D16" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="51"/>
-      <c r="L16" s="51"/>
-      <c r="M16" s="51"/>
-      <c r="N16" s="51"/>
-      <c r="O16" s="51"/>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="41"/>
-    </row>
-    <row r="17" spans="1:17">
-      <c r="A17" s="41"/>
-      <c r="B17" s="41" t="s">
-        <v>297</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>298</v>
-      </c>
-      <c r="D17" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" s="41" t="s">
-        <v>188</v>
-      </c>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="51"/>
-      <c r="L17" s="51"/>
-      <c r="M17" s="51"/>
-      <c r="N17" s="51"/>
-      <c r="O17" s="51"/>
-      <c r="P17" s="41"/>
-      <c r="Q17" s="41"/>
-    </row>
-    <row r="18" spans="1:17">
-      <c r="A18" s="41"/>
-      <c r="B18" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="51"/>
-      <c r="L18" s="51"/>
-      <c r="M18" s="51"/>
-      <c r="N18" s="51"/>
-      <c r="O18" s="51"/>
-      <c r="P18" s="41"/>
-      <c r="Q18" s="41"/>
-    </row>
-    <row r="19" spans="1:17">
-      <c r="A19" s="41"/>
-      <c r="B19" s="41"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="51"/>
-      <c r="L19" s="51"/>
-      <c r="M19" s="51"/>
-      <c r="N19" s="51"/>
-      <c r="O19" s="51"/>
-      <c r="P19" s="41"/>
-      <c r="Q19" s="41"/>
-    </row>
-    <row r="20" spans="1:17">
-      <c r="A20" s="41"/>
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="51"/>
-      <c r="K20" s="51"/>
-      <c r="L20" s="51"/>
-      <c r="M20" s="51"/>
-      <c r="N20" s="51"/>
-      <c r="O20" s="51"/>
-      <c r="P20" s="41"/>
-      <c r="Q20" s="41"/>
-    </row>
-    <row r="21" spans="1:17">
-      <c r="A21" s="41"/>
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="51"/>
-      <c r="L21" s="51"/>
-      <c r="M21" s="51"/>
-      <c r="N21" s="51"/>
-      <c r="O21" s="51"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="41"/>
-    </row>
-    <row r="22" spans="1:17">
-      <c r="A22" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="B22" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="C22" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="E22" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="51"/>
-      <c r="K22" s="51"/>
-      <c r="L22" s="51"/>
-      <c r="M22" s="51"/>
-      <c r="N22" s="51"/>
-      <c r="O22" s="51"/>
-      <c r="P22" s="41"/>
-      <c r="Q22" s="41"/>
-    </row>
-    <row r="23" spans="1:17" ht="34.950000000000003" customHeight="1">
-      <c r="A23" s="41"/>
-      <c r="B23" s="52" t="s">
-        <v>124</v>
-      </c>
-      <c r="C23" s="53" t="s">
-        <v>125</v>
-      </c>
-      <c r="D23" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="E23" s="54" t="s">
-        <v>349</v>
-      </c>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="51"/>
-      <c r="L23" s="51"/>
-      <c r="M23" s="51"/>
-      <c r="N23" s="51"/>
-      <c r="O23" s="51"/>
-      <c r="P23" s="41"/>
-      <c r="Q23" s="41"/>
-    </row>
-    <row r="24" spans="1:17">
-      <c r="A24" s="41"/>
-      <c r="B24" s="52"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="F24" s="56"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="41"/>
-      <c r="J24" s="51"/>
-      <c r="K24" s="51"/>
-      <c r="L24" s="51"/>
-      <c r="M24" s="51"/>
-      <c r="N24" s="51"/>
-      <c r="O24" s="51"/>
-      <c r="P24" s="41"/>
-      <c r="Q24" s="41"/>
-    </row>
-    <row r="25" spans="1:17">
-      <c r="A25" s="41"/>
-      <c r="B25" s="56" t="s">
-        <v>291</v>
-      </c>
-      <c r="C25" s="56" t="s">
-        <v>330</v>
-      </c>
-      <c r="D25" s="56" t="s">
-        <v>56</v>
-      </c>
-      <c r="E25" s="56" t="s">
-        <v>166</v>
-      </c>
-      <c r="F25" s="56"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="41"/>
-      <c r="M25" s="41"/>
-      <c r="N25" s="41"/>
-      <c r="O25" s="41"/>
-      <c r="P25" s="41"/>
-      <c r="Q25" s="41"/>
-    </row>
-    <row r="26" spans="1:17">
-      <c r="A26" s="41"/>
-      <c r="B26" s="56" t="s">
-        <v>293</v>
-      </c>
-      <c r="C26" s="56" t="s">
-        <v>331</v>
-      </c>
-      <c r="D26" s="56" t="s">
-        <v>67</v>
-      </c>
-      <c r="E26" s="56" t="s">
-        <v>79</v>
-      </c>
-      <c r="F26" s="56"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="K26" s="57"/>
-      <c r="L26" s="57"/>
-      <c r="M26" s="57"/>
-      <c r="N26" s="41"/>
-      <c r="O26" s="41"/>
-      <c r="P26" s="41"/>
-      <c r="Q26" s="41"/>
-    </row>
-    <row r="27" spans="1:17">
-      <c r="A27" s="41"/>
-      <c r="B27" s="56" t="s">
-        <v>351</v>
-      </c>
-      <c r="C27" s="56" t="s">
-        <v>302</v>
-      </c>
-      <c r="D27" s="56" t="s">
-        <v>56</v>
-      </c>
-      <c r="E27" s="56" t="s">
-        <v>136</v>
-      </c>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="57"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="57"/>
-      <c r="M27" s="57"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="41"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-    </row>
-    <row r="28" spans="1:17">
-      <c r="A28" s="41"/>
-      <c r="B28" s="56" t="s">
-        <v>352</v>
-      </c>
-      <c r="C28" s="56" t="s">
-        <v>305</v>
-      </c>
-      <c r="D28" s="56" t="s">
-        <v>67</v>
-      </c>
-      <c r="E28" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="57"/>
-      <c r="K28" s="57"/>
-      <c r="L28" s="57"/>
-      <c r="M28" s="57"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="41"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="54"/>
+      <c r="K28" s="54"/>
+      <c r="L28" s="54"/>
+      <c r="M28" s="54"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="35"/>
+      <c r="P28" s="35"/>
+      <c r="Q28" s="35"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="41"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="41"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="41"/>
-      <c r="M29" s="41"/>
-      <c r="N29" s="41"/>
-      <c r="O29" s="41"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
+      <c r="A29" s="35"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="35"/>
+      <c r="P29" s="35"/>
+      <c r="Q29" s="35"/>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="41"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="41"/>
-      <c r="K30" s="41"/>
-      <c r="L30" s="41"/>
-      <c r="M30" s="41"/>
-      <c r="N30" s="41"/>
-      <c r="O30" s="41"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
+      <c r="A30" s="35"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
+      <c r="N30" s="35"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="35"/>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="41"/>
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
-      <c r="K31" s="41"/>
-      <c r="L31" s="41"/>
-      <c r="M31" s="41"/>
-      <c r="N31" s="41"/>
-      <c r="O31" s="41"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
+      <c r="A31" s="35"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
     </row>
     <row r="32" spans="1:17">
-      <c r="A32" s="41"/>
-      <c r="B32" s="41"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="41"/>
-      <c r="I32" s="41"/>
-      <c r="J32" s="41"/>
-      <c r="K32" s="41"/>
-      <c r="L32" s="41"/>
-      <c r="M32" s="41"/>
-      <c r="N32" s="41"/>
-      <c r="O32" s="41"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
+      <c r="A32" s="35"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="35"/>
+      <c r="N32" s="35"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5681,381 +5721,381 @@
   <dimension ref="A1:O23"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="41"/>
-    <col min="2" max="2" width="14" style="41" customWidth="1"/>
-    <col min="3" max="16384" width="8.77734375" style="41"/>
+    <col min="1" max="1" width="8.77734375" style="35"/>
+    <col min="2" max="2" width="14" style="35" customWidth="1"/>
+    <col min="3" max="16384" width="8.77734375" style="35"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="41" t="s">
-        <v>299</v>
+      <c r="A1" s="35" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="41" t="s">
-        <v>53</v>
+      <c r="A3" s="35" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:15">
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="41" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="5" spans="1:15">
-      <c r="B5" s="42" t="s">
-        <v>291</v>
-      </c>
-      <c r="C5" s="41" t="s">
+      <c r="B5" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>329</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="B6" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="C6" s="35" t="s">
         <v>330</v>
       </c>
-      <c r="D5" s="41" t="s">
+      <c r="D6" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="B7" s="37" t="s">
+        <v>331</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>332</v>
+      </c>
+      <c r="D7" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="B8" s="36"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="35" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="B11" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="B12" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="B13" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>329</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="B14" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>330</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="40"/>
+      <c r="M14" s="40"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="40"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="B15" s="35" t="s">
+        <v>334</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="G15" s="59" t="s">
+        <v>335</v>
+      </c>
+      <c r="H15" s="52"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="52"/>
+      <c r="K15" s="52"/>
+      <c r="L15" s="52"/>
+      <c r="M15" s="52"/>
+      <c r="N15" s="52"/>
+      <c r="O15" s="52"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="B16" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="52"/>
+      <c r="K16" s="52"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="52"/>
+      <c r="O16" s="52"/>
+    </row>
+    <row r="17" spans="2:15">
+      <c r="B17" s="35" t="s">
+        <v>300</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>301</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="52"/>
+      <c r="O17" s="52"/>
+    </row>
+    <row r="18" spans="2:15">
+      <c r="B18" s="35" t="s">
+        <v>336</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="D18" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
+      <c r="K18" s="52"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="52"/>
+      <c r="O18" s="52"/>
+    </row>
+    <row r="19" spans="2:15">
+      <c r="B19" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>338</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
+      <c r="K19" s="52"/>
+      <c r="L19" s="52"/>
+      <c r="M19" s="52"/>
+      <c r="N19" s="52"/>
+      <c r="O19" s="52"/>
+    </row>
+    <row r="20" spans="2:15">
+      <c r="B20" s="35" t="s">
+        <v>339</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>340</v>
+      </c>
+      <c r="D20" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="41" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="B6" s="42" t="s">
-        <v>293</v>
-      </c>
-      <c r="C6" s="41" t="s">
-        <v>331</v>
-      </c>
-      <c r="D6" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="41" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="B7" s="43" t="s">
-        <v>332</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>333</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="44" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="41" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="B8" s="42"/>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="41" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="B11" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="C11" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="D11" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="46"/>
-      <c r="N11" s="46"/>
-      <c r="O11" s="46"/>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="B12" s="41" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" s="41" t="s">
-        <v>125</v>
-      </c>
-      <c r="D12" s="41" t="s">
-        <v>126</v>
-      </c>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="46"/>
-      <c r="N12" s="46"/>
-      <c r="O12" s="46"/>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="B13" s="42" t="s">
-        <v>291</v>
-      </c>
-      <c r="C13" s="41" t="s">
-        <v>330</v>
-      </c>
-      <c r="D13" s="41" t="s">
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="52"/>
+      <c r="K20" s="52"/>
+      <c r="L20" s="52"/>
+      <c r="M20" s="52"/>
+      <c r="N20" s="52"/>
+      <c r="O20" s="52"/>
+    </row>
+    <row r="21" spans="2:15">
+      <c r="B21" s="35" t="s">
+        <v>341</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>342</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="41" t="s">
-        <v>166</v>
-      </c>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="46"/>
-      <c r="O13" s="46"/>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="B14" s="42" t="s">
-        <v>293</v>
-      </c>
-      <c r="C14" s="41" t="s">
-        <v>331</v>
-      </c>
-      <c r="D14" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
-      <c r="N14" s="46"/>
-      <c r="O14" s="46"/>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="B15" s="41" t="s">
-        <v>335</v>
-      </c>
-      <c r="C15" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="41" t="s">
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="52"/>
+      <c r="K21" s="52"/>
+      <c r="L21" s="52"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="52"/>
+      <c r="O21" s="52"/>
+    </row>
+    <row r="22" spans="2:15">
+      <c r="B22" s="35" t="s">
+        <v>343</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>344</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="52"/>
+      <c r="K22" s="52"/>
+      <c r="L22" s="52"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="52"/>
+      <c r="O22" s="52"/>
+    </row>
+    <row r="23" spans="2:15">
+      <c r="B23" s="35" t="s">
+        <v>345</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>346</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="G15" s="47" t="s">
-        <v>336</v>
-      </c>
-      <c r="H15" s="37"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="37"/>
-      <c r="L15" s="37"/>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
-      <c r="O15" s="37"/>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="B16" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="37"/>
-      <c r="L16" s="37"/>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-    </row>
-    <row r="17" spans="2:15">
-      <c r="B17" s="41" t="s">
-        <v>301</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>302</v>
-      </c>
-      <c r="D17" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="37"/>
-      <c r="L17" s="37"/>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-    </row>
-    <row r="18" spans="2:15">
-      <c r="B18" s="41" t="s">
-        <v>337</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>305</v>
-      </c>
-      <c r="D18" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="37"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-    </row>
-    <row r="19" spans="2:15">
-      <c r="B19" s="41" t="s">
-        <v>338</v>
-      </c>
-      <c r="C19" s="41" t="s">
-        <v>339</v>
-      </c>
-      <c r="D19" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="37"/>
-      <c r="L19" s="37"/>
-      <c r="M19" s="37"/>
-      <c r="N19" s="37"/>
-      <c r="O19" s="37"/>
-    </row>
-    <row r="20" spans="2:15">
-      <c r="B20" s="41" t="s">
-        <v>340</v>
-      </c>
-      <c r="C20" s="41" t="s">
-        <v>341</v>
-      </c>
-      <c r="D20" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="37"/>
-      <c r="L20" s="37"/>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="37"/>
-    </row>
-    <row r="21" spans="2:15">
-      <c r="B21" s="41" t="s">
-        <v>342</v>
-      </c>
-      <c r="C21" s="41" t="s">
-        <v>343</v>
-      </c>
-      <c r="D21" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="37"/>
-      <c r="L21" s="37"/>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-    </row>
-    <row r="22" spans="2:15">
-      <c r="B22" s="41" t="s">
-        <v>344</v>
-      </c>
-      <c r="C22" s="41" t="s">
-        <v>345</v>
-      </c>
-      <c r="D22" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="37"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-    </row>
-    <row r="23" spans="2:15">
-      <c r="B23" s="41" t="s">
-        <v>346</v>
-      </c>
-      <c r="C23" s="41" t="s">
-        <v>347</v>
-      </c>
-      <c r="D23" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E23" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="37"/>
-      <c r="N23" s="37"/>
-      <c r="O23" s="37"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="52"/>
+      <c r="K23" s="52"/>
+      <c r="L23" s="52"/>
+      <c r="M23" s="52"/>
+      <c r="N23" s="52"/>
+      <c r="O23" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6077,169 +6117,169 @@
     <col min="4" max="16384" width="8.77734375" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="41" customFormat="1">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:11" s="35" customFormat="1">
+      <c r="A1" s="35" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="35" customFormat="1">
+      <c r="B2" s="35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="35" customFormat="1"/>
+    <row r="4" spans="1:11" s="35" customFormat="1">
+      <c r="A4" s="35" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="35" customFormat="1">
+      <c r="B5" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+    </row>
+    <row r="6" spans="1:11" s="35" customFormat="1">
+      <c r="B6" s="42" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" s="41" customFormat="1">
-      <c r="B2" s="41" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="41" customFormat="1"/>
-    <row r="4" spans="1:11" s="41" customFormat="1">
-      <c r="A4" s="41" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="41" customFormat="1">
-      <c r="B5" s="49" t="s">
-        <v>129</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="D5" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5" s="50" t="s">
-        <v>348</v>
-      </c>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-    </row>
-    <row r="6" spans="1:11" s="41" customFormat="1">
-      <c r="B6" s="49" t="s">
+      <c r="C6" s="35" t="s">
         <v>301</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="D6" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="G6" s="52" t="s">
         <v>302</v>
       </c>
-      <c r="D6" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="G6" s="37" t="s">
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+    </row>
+    <row r="7" spans="1:11" s="35" customFormat="1">
+      <c r="B7" s="42" t="s">
         <v>303</v>
       </c>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="37"/>
-    </row>
-    <row r="7" spans="1:11" s="41" customFormat="1">
-      <c r="B7" s="49" t="s">
+      <c r="C7" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="D7" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="52"/>
+    </row>
+    <row r="8" spans="1:11" s="35" customFormat="1">
+      <c r="B8" s="35" t="s">
         <v>305</v>
       </c>
-      <c r="D7" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="37"/>
-    </row>
-    <row r="8" spans="1:11" s="41" customFormat="1">
-      <c r="B8" s="41" t="s">
+      <c r="C8" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="52"/>
+    </row>
+    <row r="9" spans="1:11" s="35" customFormat="1">
+      <c r="B9" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
+      <c r="K9" s="52"/>
+    </row>
+    <row r="10" spans="1:11" s="35" customFormat="1">
+      <c r="B10" s="35" t="s">
         <v>306</v>
       </c>
-      <c r="C8" s="41" t="s">
-        <v>194</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
-    </row>
-    <row r="9" spans="1:11" s="41" customFormat="1">
-      <c r="B9" s="41" t="s">
-        <v>152</v>
-      </c>
-      <c r="C9" s="41" t="s">
-        <v>153</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-    </row>
-    <row r="10" spans="1:11" s="41" customFormat="1">
-      <c r="B10" s="41" t="s">
-        <v>307</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E10" s="41" t="s">
-        <v>157</v>
-      </c>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-    </row>
-    <row r="11" spans="1:11" s="41" customFormat="1"/>
-    <row r="12" spans="1:11" s="41" customFormat="1">
-      <c r="A12" s="41" t="s">
+      <c r="C10" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="52"/>
+    </row>
+    <row r="11" spans="1:11" s="35" customFormat="1"/>
+    <row r="12" spans="1:11" s="35" customFormat="1">
+      <c r="A12" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="B12" s="45" t="s">
+      <c r="C12" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="C12" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="D12" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="41">
+      <c r="D12" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="35">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="41" customFormat="1">
-      <c r="B13" s="58" t="s">
+    <row r="13" spans="1:11" s="35" customFormat="1">
+      <c r="B13" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="45" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="58" t="s">
-        <v>125</v>
-      </c>
-      <c r="D13" s="58" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="41">
+      <c r="D13" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="35">
         <v>220</v>
       </c>
     </row>
@@ -6263,149 +6303,149 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
+      <c r="A1" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="41"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="41" t="s">
-        <v>308</v>
-      </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
+      <c r="A3" s="35" t="s">
+        <v>307</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="41"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="59" t="s">
-        <v>353</v>
-      </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
+      <c r="A5" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>352</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="41"/>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="C7" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="41">
+      <c r="D7" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="35">
         <v>1</v>
       </c>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="41"/>
-      <c r="B8" s="58" t="s">
+      <c r="A8" s="35"/>
+      <c r="B8" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="45" t="s">
         <v>124</v>
       </c>
-      <c r="C8" s="58" t="s">
-        <v>125</v>
-      </c>
-      <c r="D8" s="58" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="41">
+      <c r="D8" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="35">
         <v>220</v>
       </c>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="41"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/aspnet-core/prototype/领用配送接口FS(2).xlsx
+++ b/aspnet-core/prototype/领用配送接口FS(2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\module-zero-core-template\aspnet-core\prototype\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7CDA271-C138-473E-84D6-945F7EC2FA34}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B18FB07-DF28-44D9-942E-3A9507D7F3B1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6948" tabRatio="669" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6948" tabRatio="669" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="目录" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="364">
   <si>
     <t>A-LM-ABAP-WMZC588</t>
   </si>
@@ -1248,6 +1248,26 @@
   </si>
   <si>
     <t>25,0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LGORT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHAR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LGNUM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,0</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1520,7 +1540,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1691,6 +1711,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5048,8 +5074,8 @@
       <c r="D6" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="35" t="s">
-        <v>78</v>
+      <c r="E6" s="63" t="s">
+        <v>359</v>
       </c>
       <c r="F6" s="35" t="s">
         <v>293</v>
@@ -5233,9 +5259,15 @@
       <c r="B13" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
+      <c r="C13" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="D13" s="64" t="s">
+        <v>361</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>56</v>
+      </c>
       <c r="F13" s="35"/>
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
@@ -5254,9 +5286,15 @@
       <c r="B14" s="35" t="s">
         <v>140</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
+      <c r="C14" s="64" t="s">
+        <v>362</v>
+      </c>
+      <c r="D14" s="63" t="s">
+        <v>361</v>
+      </c>
+      <c r="E14" s="64" t="s">
+        <v>363</v>
+      </c>
       <c r="F14" s="35"/>
       <c r="G14" s="35"/>
       <c r="H14" s="35"/>
@@ -5774,8 +5812,8 @@
       <c r="D6" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="35" t="s">
-        <v>78</v>
+      <c r="E6" s="63" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="7" spans="1:15">
